--- a/research/traditional_assets/database/data/argentina/argentina_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_real_estate_development.xlsx
@@ -588,43 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.799</v>
+        <v>-0.0584</v>
+      </c>
+      <c r="E2">
+        <v>0.226</v>
       </c>
       <c r="G2">
-        <v>0.1532524807056229</v>
+        <v>0.4269081500646831</v>
       </c>
       <c r="H2">
-        <v>0.1532524807056229</v>
+        <v>0.4269081500646831</v>
       </c>
       <c r="I2">
-        <v>0.2061742006615215</v>
+        <v>-0.1234152652005175</v>
       </c>
       <c r="J2">
-        <v>0.1030871003307607</v>
+        <v>-0.1129436669410796</v>
       </c>
       <c r="K2">
-        <v>-58.5</v>
+        <v>39.4</v>
       </c>
       <c r="L2">
-        <v>-0.6449834619625138</v>
+        <v>0.5097024579560155</v>
       </c>
       <c r="M2">
-        <v>55.5</v>
+        <v>27.0534</v>
       </c>
       <c r="N2">
-        <v>0.0604970568999346</v>
+        <v>0.02620945553187367</v>
       </c>
       <c r="O2">
-        <v>-0.9487179487179487</v>
+        <v>0.6866345177664975</v>
       </c>
       <c r="P2">
-        <v>55.5</v>
+        <v>27.0534</v>
       </c>
       <c r="Q2">
-        <v>0.0604970568999346</v>
+        <v>0.02620945553187367</v>
       </c>
       <c r="R2">
-        <v>-0.9487179487179487</v>
+        <v>0.6866345177664975</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,70 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>28.4</v>
+        <v>11.3</v>
       </c>
       <c r="V2">
-        <v>0.03095705253978635</v>
+        <v>0.0109474907963573</v>
       </c>
       <c r="W2">
-        <v>-0.1303185564713745</v>
+        <v>0.09227166276346604</v>
       </c>
       <c r="X2">
-        <v>0.09828669843300905</v>
+        <v>0.1747719332986604</v>
       </c>
       <c r="Y2">
-        <v>-0.2286052549043835</v>
+        <v>-0.08250027053519438</v>
       </c>
       <c r="Z2">
-        <v>0.2244493937144272</v>
+        <v>0.185327259649964</v>
       </c>
       <c r="AA2">
-        <v>0.02313783716901757</v>
+        <v>-0.02093154028900852</v>
       </c>
       <c r="AB2">
-        <v>0.0982035253623396</v>
+        <v>0.1742227451078739</v>
       </c>
       <c r="AC2">
-        <v>-0.07506568819332203</v>
+        <v>-0.1951542853968825</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>11.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18.5</v>
+        <v>11.8</v>
       </c>
       <c r="AG2">
-        <v>-9.899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AH2">
-        <v>0.01976706913131745</v>
+        <v>0.01130268199233717</v>
       </c>
       <c r="AI2">
-        <v>0.03352056531980432</v>
+        <v>0.01997629930590825</v>
       </c>
       <c r="AJ2">
-        <v>-0.01090909090909091</v>
+        <v>0.0004841677156967173</v>
       </c>
       <c r="AK2">
-        <v>-0.01891117478510028</v>
+        <v>0.0008629616845012082</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="AM2">
-        <v>-0.619</v>
+        <v>-1.375</v>
       </c>
       <c r="AN2">
-        <v>0.83710407239819</v>
+        <v>-1.18</v>
+      </c>
+      <c r="AO2">
+        <v>-127.2</v>
       </c>
       <c r="AP2">
-        <v>-0.4479638009049773</v>
+        <v>-0.05</v>
       </c>
       <c r="AQ2">
-        <v>-30.21001615508885</v>
+        <v>6.938181818181818</v>
       </c>
     </row>
     <row r="3">
@@ -716,43 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.799</v>
+        <v>-0.0584</v>
+      </c>
+      <c r="E3">
+        <v>0.226</v>
       </c>
       <c r="G3">
-        <v>0.1532524807056229</v>
+        <v>0.4269081500646831</v>
       </c>
       <c r="H3">
-        <v>0.1532524807056229</v>
+        <v>0.4269081500646831</v>
       </c>
       <c r="I3">
-        <v>0.2061742006615215</v>
+        <v>-0.1234152652005175</v>
       </c>
       <c r="J3">
-        <v>0.1030871003307607</v>
+        <v>-0.1129436669410796</v>
       </c>
       <c r="K3">
-        <v>-58.5</v>
+        <v>39.4</v>
       </c>
       <c r="L3">
-        <v>-0.6449834619625138</v>
+        <v>0.5097024579560155</v>
       </c>
       <c r="M3">
-        <v>55.5</v>
+        <v>27.0534</v>
       </c>
       <c r="N3">
-        <v>0.0604970568999346</v>
+        <v>0.02620945553187367</v>
       </c>
       <c r="O3">
-        <v>-0.9487179487179487</v>
+        <v>0.6866345177664975</v>
       </c>
       <c r="P3">
-        <v>55.5</v>
+        <v>27.0534</v>
       </c>
       <c r="Q3">
-        <v>0.0604970568999346</v>
+        <v>0.02620945553187367</v>
       </c>
       <c r="R3">
-        <v>-0.9487179487179487</v>
+        <v>0.6866345177664975</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,70 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>28.4</v>
+        <v>11.3</v>
       </c>
       <c r="V3">
-        <v>0.03095705253978635</v>
+        <v>0.0109474907963573</v>
       </c>
       <c r="W3">
-        <v>-0.1303185564713745</v>
+        <v>0.09227166276346604</v>
       </c>
       <c r="X3">
-        <v>0.09828669843300905</v>
+        <v>0.1747719332986604</v>
       </c>
       <c r="Y3">
-        <v>-0.2286052549043835</v>
+        <v>-0.08250027053519438</v>
       </c>
       <c r="Z3">
-        <v>0.2244493937144272</v>
+        <v>0.185327259649964</v>
       </c>
       <c r="AA3">
-        <v>0.02313783716901757</v>
+        <v>-0.02093154028900852</v>
       </c>
       <c r="AB3">
-        <v>0.0982035253623396</v>
+        <v>0.1742227451078739</v>
       </c>
       <c r="AC3">
-        <v>-0.07506568819332203</v>
+        <v>-0.1951542853968825</v>
       </c>
       <c r="AD3">
-        <v>18.5</v>
+        <v>11.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18.5</v>
+        <v>11.8</v>
       </c>
       <c r="AG3">
-        <v>-9.899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AH3">
-        <v>0.01976706913131745</v>
+        <v>0.01130268199233717</v>
       </c>
       <c r="AI3">
-        <v>0.03352056531980432</v>
+        <v>0.01997629930590825</v>
       </c>
       <c r="AJ3">
-        <v>-0.01090909090909091</v>
+        <v>0.0004841677156967173</v>
       </c>
       <c r="AK3">
-        <v>-0.01891117478510028</v>
+        <v>0.0008629616845012082</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="AM3">
-        <v>-0.619</v>
+        <v>-1.375</v>
       </c>
       <c r="AN3">
-        <v>0.83710407239819</v>
+        <v>-1.18</v>
+      </c>
+      <c r="AO3">
+        <v>-127.2</v>
       </c>
       <c r="AP3">
-        <v>-0.4479638009049773</v>
+        <v>-0.05</v>
       </c>
       <c r="AQ3">
-        <v>-30.21001615508885</v>
+        <v>6.938181818181818</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/argentina/argentina_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_real_estate_development.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="base_ctio" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,121 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0584</v>
+        <v>0.263</v>
       </c>
       <c r="E2">
-        <v>0.226</v>
+        <v>0.186</v>
       </c>
       <c r="G2">
-        <v>0.4269081500646831</v>
+        <v>0.1418581418581419</v>
       </c>
       <c r="H2">
-        <v>0.4269081500646831</v>
+        <v>0.1418581418581419</v>
       </c>
       <c r="I2">
-        <v>-0.1234152652005175</v>
+        <v>0.1208791208791209</v>
       </c>
       <c r="J2">
-        <v>-0.1129436669410796</v>
+        <v>0.1033008975757067</v>
       </c>
       <c r="K2">
-        <v>39.4</v>
+        <v>46.9</v>
       </c>
       <c r="L2">
-        <v>0.5097024579560155</v>
+        <v>0.4685314685314685</v>
       </c>
       <c r="M2">
-        <v>27.0534</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.02620945553187367</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.6866345177664975</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>27.0534</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.02620945553187367</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.6866345177664975</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>11.3</v>
+        <v>20.3</v>
       </c>
       <c r="V2">
-        <v>0.0109474907963573</v>
+        <v>0.02849522740033689</v>
       </c>
       <c r="W2">
-        <v>0.09227166276346604</v>
+        <v>0.09626436781609195</v>
       </c>
       <c r="X2">
-        <v>0.1747719332986604</v>
+        <v>0.1393332357838906</v>
       </c>
       <c r="Y2">
-        <v>-0.08250027053519438</v>
+        <v>-0.04306886796779867</v>
       </c>
       <c r="Z2">
-        <v>0.185327259649964</v>
+        <v>0.205249128562641</v>
       </c>
       <c r="AA2">
-        <v>-0.02093154028900852</v>
+        <v>0.02120241920715244</v>
       </c>
       <c r="AB2">
-        <v>0.1742227451078739</v>
+        <v>0.138798943362478</v>
       </c>
       <c r="AC2">
-        <v>-0.1951542853968825</v>
+        <v>-0.1175965241553256</v>
       </c>
       <c r="AD2">
-        <v>11.8</v>
+        <v>20</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.8</v>
+        <v>20</v>
       </c>
       <c r="AG2">
-        <v>0.5</v>
+        <v>-0.3000000000000007</v>
       </c>
       <c r="AH2">
-        <v>0.01130268199233717</v>
+        <v>0.02730748225013654</v>
       </c>
       <c r="AI2">
-        <v>0.01997629930590825</v>
+        <v>0.03221649484536083</v>
       </c>
       <c r="AJ2">
-        <v>0.0004841677156967173</v>
+        <v>-0.0004212891447830371</v>
       </c>
       <c r="AK2">
-        <v>0.0008629616845012082</v>
+        <v>-0.0004995836802664458</v>
       </c>
       <c r="AL2">
-        <v>0.075</v>
+        <v>0.36</v>
       </c>
       <c r="AM2">
-        <v>-1.375</v>
+        <v>-1.24</v>
       </c>
       <c r="AN2">
-        <v>-1.18</v>
+        <v>1.526717557251908</v>
       </c>
       <c r="AO2">
-        <v>-127.2</v>
+        <v>33.61111111111111</v>
       </c>
       <c r="AP2">
-        <v>-0.05</v>
+        <v>-0.02290076335877868</v>
       </c>
       <c r="AQ2">
-        <v>6.938181818181818</v>
+        <v>-9.75806451612903</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +721,8890 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0584</v>
+        <v>0.263</v>
       </c>
       <c r="E3">
-        <v>0.226</v>
+        <v>0.186</v>
       </c>
       <c r="G3">
-        <v>0.4269081500646831</v>
+        <v>0.1418581418581419</v>
       </c>
       <c r="H3">
-        <v>0.4269081500646831</v>
+        <v>0.1418581418581419</v>
       </c>
       <c r="I3">
-        <v>-0.1234152652005175</v>
+        <v>0.1208791208791209</v>
       </c>
       <c r="J3">
-        <v>-0.1129436669410796</v>
+        <v>0.1033008975757067</v>
       </c>
       <c r="K3">
-        <v>39.4</v>
+        <v>46.9</v>
       </c>
       <c r="L3">
-        <v>0.5097024579560155</v>
+        <v>0.4685314685314685</v>
       </c>
       <c r="M3">
-        <v>27.0534</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.02620945553187367</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.6866345177664975</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>27.0534</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.02620945553187367</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.6866345177664975</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="U3">
+        <v>20.3</v>
+      </c>
+      <c r="V3">
+        <v>0.02849522740033689</v>
+      </c>
+      <c r="W3">
+        <v>0.09626436781609195</v>
+      </c>
+      <c r="X3">
+        <v>0.1393332357838906</v>
+      </c>
+      <c r="Y3">
+        <v>-0.04306886796779867</v>
+      </c>
+      <c r="Z3">
+        <v>0.205249128562641</v>
+      </c>
+      <c r="AA3">
+        <v>0.02120241920715244</v>
+      </c>
+      <c r="AB3">
+        <v>0.138798943362478</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1175965241553256</v>
+      </c>
+      <c r="AD3">
+        <v>20</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>20</v>
+      </c>
+      <c r="AG3">
+        <v>-0.3000000000000007</v>
+      </c>
+      <c r="AH3">
+        <v>0.02730748225013654</v>
+      </c>
+      <c r="AI3">
+        <v>0.03221649484536083</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.0004212891447830371</v>
+      </c>
+      <c r="AK3">
+        <v>-0.0004995836802664458</v>
+      </c>
+      <c r="AL3">
+        <v>0.36</v>
+      </c>
+      <c r="AM3">
+        <v>-1.24</v>
+      </c>
+      <c r="AN3">
+        <v>1.526717557251908</v>
+      </c>
+      <c r="AO3">
+        <v>33.61111111111111</v>
+      </c>
+      <c r="AP3">
+        <v>-0.02290076335877868</v>
+      </c>
+      <c r="AQ3">
+        <v>-9.75806451612903</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Consultatio S.A. (BASE:CTIO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BASE:CTIO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Real Estate (Development)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>33.6111111111111</v>
+      </c>
+      <c r="F2">
+        <v>3.0142358623121</v>
+      </c>
+      <c r="G2">
+        <v>1.52671755725191</v>
+      </c>
+      <c r="H2">
+        <v>5.03175572519084</v>
+      </c>
+      <c r="I2">
+        <v>0.0273074822501365</v>
+      </c>
+      <c r="J2">
+        <v>0.09</v>
+      </c>
+      <c r="K2">
+        <v>712.4</v>
+      </c>
+      <c r="L2">
+        <v>698.5331516359601</v>
+      </c>
+      <c r="M2">
+        <v>712.1</v>
+      </c>
+      <c r="N2">
+        <v>744.14915163596</v>
+      </c>
+      <c r="O2">
+        <v>20</v>
+      </c>
+      <c r="P2">
+        <v>65.916</v>
+      </c>
+      <c r="Q2">
+        <v>0.138798943362478</v>
+      </c>
+      <c r="R2">
+        <v>0.134492170597617</v>
+      </c>
+      <c r="S2">
+        <v>0.119767447311761</v>
+      </c>
+      <c r="T2">
+        <v>0.039585</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.139333235783891</v>
+      </c>
+      <c r="X2">
+        <v>0.143878594063316</v>
+      </c>
+      <c r="Y2">
+        <v>0.453870606562232</v>
+      </c>
+      <c r="Z2">
+        <v>0.474391228456469</v>
+      </c>
+      <c r="AA2">
+        <v>20</v>
+      </c>
+      <c r="AB2">
+        <v>0.1842576112488635</v>
+      </c>
+      <c r="AC2">
+        <v>33.61111111111111</v>
+      </c>
+      <c r="AD2">
+        <v>20</v>
+      </c>
+      <c r="AE2">
+        <v>0.36</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>13.1</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>712.4</v>
+      </c>
+      <c r="AK2">
+        <v>0.2215019750791156</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.35</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>1.404999999999998</v>
+      </c>
+      <c r="AR2">
+        <v>0.36</v>
+      </c>
+      <c r="AS2">
+        <v>20</v>
+      </c>
+      <c r="AT2">
+        <v>20.3</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1375315648917062</v>
+      </c>
+      <c r="C2">
+        <v>741.5409490979558</v>
+      </c>
+      <c r="D2">
+        <v>721.2409490979559</v>
+      </c>
+      <c r="E2">
+        <v>-20</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>20.3</v>
+      </c>
+      <c r="H2">
+        <v>712.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>13.1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>12.1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>12.1</v>
+      </c>
+      <c r="O2">
+        <v>4.234999999999999</v>
+      </c>
+      <c r="P2">
+        <v>7.865</v>
+      </c>
+      <c r="Q2">
+        <v>8.865</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1375315648917062</v>
+      </c>
+      <c r="T2">
+        <v>0.4457367247241993</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.35</v>
+      </c>
+      <c r="W2">
+        <v>0.029055</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1370885544145852</v>
+      </c>
+      <c r="C3">
+        <v>737.4677578913312</v>
+      </c>
+      <c r="D3">
+        <v>724.4917578913312</v>
+      </c>
+      <c r="E3">
+        <v>-12.676</v>
+      </c>
+      <c r="F3">
+        <v>7.324</v>
+      </c>
+      <c r="G3">
+        <v>20.3</v>
+      </c>
+      <c r="H3">
+        <v>712.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>13.1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>12.1</v>
+      </c>
+      <c r="M3">
+        <v>0.3273828</v>
+      </c>
+      <c r="N3">
+        <v>11.7726172</v>
+      </c>
+      <c r="O3">
+        <v>4.12041602</v>
+      </c>
+      <c r="P3">
+        <v>7.65220118</v>
+      </c>
+      <c r="Q3">
+        <v>8.652201179999999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.138179802438975</v>
+      </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.448663278977439</v>
       </c>
       <c r="U3">
-        <v>11.3</v>
+        <v>0.0447</v>
       </c>
       <c r="V3">
-        <v>0.0109474907963573</v>
+        <v>0.35</v>
       </c>
       <c r="W3">
-        <v>0.09227166276346604</v>
-      </c>
-      <c r="X3">
-        <v>0.1747719332986604</v>
+        <v>0.029055</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.08250027053519438</v>
+        <v>36.95979141237719</v>
       </c>
       <c r="Z3">
-        <v>0.185327259649964</v>
-      </c>
-      <c r="AA3">
-        <v>-0.02093154028900852</v>
-      </c>
-      <c r="AB3">
-        <v>0.1742227451078739</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1951542853968825</v>
-      </c>
-      <c r="AD3">
-        <v>11.8</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>11.8</v>
-      </c>
-      <c r="AG3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1366455439374643</v>
+      </c>
+      <c r="C4">
+        <v>733.424003740225</v>
+      </c>
+      <c r="D4">
+        <v>727.772003740225</v>
+      </c>
+      <c r="E4">
+        <v>-5.352</v>
+      </c>
+      <c r="F4">
+        <v>14.648</v>
+      </c>
+      <c r="G4">
+        <v>20.3</v>
+      </c>
+      <c r="H4">
+        <v>712.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>13.1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>12.1</v>
+      </c>
+      <c r="M4">
+        <v>0.6547656000000001</v>
+      </c>
+      <c r="N4">
+        <v>11.4452344</v>
+      </c>
+      <c r="O4">
+        <v>4.00583204</v>
+      </c>
+      <c r="P4">
+        <v>7.439402360000001</v>
+      </c>
+      <c r="Q4">
+        <v>8.439402360000001</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1388412693239431</v>
+      </c>
+      <c r="T4">
+        <v>0.4516495588276836</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.35</v>
+      </c>
+      <c r="W4">
+        <v>0.029055</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>18.4798957061886</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1362239834603433</v>
+      </c>
+      <c r="C5">
+        <v>729.2491247496007</v>
+      </c>
+      <c r="D5">
+        <v>730.9211247496007</v>
+      </c>
+      <c r="E5">
+        <v>1.971999999999998</v>
+      </c>
+      <c r="F5">
+        <v>21.972</v>
+      </c>
+      <c r="G5">
+        <v>20.3</v>
+      </c>
+      <c r="H5">
+        <v>712.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>13.1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>12.1</v>
+      </c>
+      <c r="M5">
+        <v>1.0063176</v>
+      </c>
+      <c r="N5">
+        <v>11.0936824</v>
+      </c>
+      <c r="O5">
+        <v>3.88278884</v>
+      </c>
+      <c r="P5">
+        <v>7.210893560000001</v>
+      </c>
+      <c r="Q5">
+        <v>8.210893560000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1395163747013848</v>
+      </c>
+      <c r="T5">
+        <v>0.4546974114583455</v>
+      </c>
+      <c r="U5">
+        <v>0.0458</v>
+      </c>
+      <c r="V5">
+        <v>0.35</v>
+      </c>
+      <c r="W5">
+        <v>0.02977</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>12.02403694420132</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1358453229832223</v>
+      </c>
+      <c r="C6">
+        <v>724.7771008503274</v>
+      </c>
+      <c r="D6">
+        <v>733.7731008503275</v>
+      </c>
+      <c r="E6">
+        <v>9.295999999999999</v>
+      </c>
+      <c r="F6">
+        <v>29.296</v>
+      </c>
+      <c r="G6">
+        <v>20.3</v>
+      </c>
+      <c r="H6">
+        <v>712.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>13.1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>12.1</v>
+      </c>
+      <c r="M6">
+        <v>1.406208</v>
+      </c>
+      <c r="N6">
+        <v>10.693792</v>
+      </c>
+      <c r="O6">
+        <v>3.7428272</v>
+      </c>
+      <c r="P6">
+        <v>6.9509648</v>
+      </c>
+      <c r="Q6">
+        <v>7.9509648</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1402055447741899</v>
+      </c>
+      <c r="T6">
+        <v>0.457808761018813</v>
+      </c>
+      <c r="U6">
+        <v>0.048</v>
+      </c>
+      <c r="V6">
+        <v>0.35</v>
+      </c>
+      <c r="W6">
+        <v>0.0312</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>8.604701438194066</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1354725125061013</v>
+      </c>
+      <c r="C7">
+        <v>720.2828431704031</v>
+      </c>
+      <c r="D7">
+        <v>736.6028431704032</v>
+      </c>
+      <c r="E7">
+        <v>16.62</v>
+      </c>
+      <c r="F7">
+        <v>36.62</v>
+      </c>
+      <c r="G7">
+        <v>20.3</v>
+      </c>
+      <c r="H7">
+        <v>712.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>13.1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>12.1</v>
+      </c>
+      <c r="M7">
+        <v>1.81269</v>
+      </c>
+      <c r="N7">
+        <v>10.28731</v>
+      </c>
+      <c r="O7">
+        <v>3.6005585</v>
+      </c>
+      <c r="P7">
+        <v>6.6867515</v>
+      </c>
+      <c r="Q7">
+        <v>7.6867515</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.140909223690633</v>
+      </c>
+      <c r="T7">
+        <v>0.4609856126752903</v>
+      </c>
+      <c r="U7">
+        <v>0.0495</v>
+      </c>
+      <c r="V7">
+        <v>0.35</v>
+      </c>
+      <c r="W7">
+        <v>0.032175</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>6.675162327811154</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1351153020289803</v>
+      </c>
+      <c r="C8">
+        <v>715.6907273831363</v>
+      </c>
+      <c r="D8">
+        <v>739.3347273831363</v>
+      </c>
+      <c r="E8">
+        <v>23.944</v>
+      </c>
+      <c r="F8">
+        <v>43.944</v>
+      </c>
+      <c r="G8">
+        <v>20.3</v>
+      </c>
+      <c r="H8">
+        <v>712.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>13.1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>12.1</v>
+      </c>
+      <c r="M8">
+        <v>2.2367496</v>
+      </c>
+      <c r="N8">
+        <v>9.8632504</v>
+      </c>
+      <c r="O8">
+        <v>3.45213764</v>
+      </c>
+      <c r="P8">
+        <v>6.41111276</v>
+      </c>
+      <c r="Q8">
+        <v>7.41111276</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1416278744989153</v>
+      </c>
+      <c r="T8">
+        <v>0.4642300569202033</v>
+      </c>
+      <c r="U8">
+        <v>0.0509</v>
+      </c>
+      <c r="V8">
+        <v>0.35</v>
+      </c>
+      <c r="W8">
+        <v>0.033085</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>5.4096354817723</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1347125915518594</v>
+      </c>
+      <c r="C9">
+        <v>711.4709896702785</v>
+      </c>
+      <c r="D9">
+        <v>742.4389896702786</v>
+      </c>
+      <c r="E9">
+        <v>31.268</v>
+      </c>
+      <c r="F9">
+        <v>51.268</v>
+      </c>
+      <c r="G9">
+        <v>20.3</v>
+      </c>
+      <c r="H9">
+        <v>712.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>13.1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>12.1</v>
+      </c>
+      <c r="M9">
+        <v>2.6095412</v>
+      </c>
+      <c r="N9">
+        <v>9.490458799999999</v>
+      </c>
+      <c r="O9">
+        <v>3.32166058</v>
+      </c>
+      <c r="P9">
+        <v>6.168798219999999</v>
+      </c>
+      <c r="Q9">
+        <v>7.168798219999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1423619801632897</v>
+      </c>
+      <c r="T9">
+        <v>0.4675442741596305</v>
+      </c>
+      <c r="U9">
+        <v>0.0509</v>
+      </c>
+      <c r="V9">
+        <v>0.35</v>
+      </c>
+      <c r="W9">
+        <v>0.033085</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>4.636830412947685</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1345854810747384</v>
+      </c>
+      <c r="C10">
+        <v>705.1322305768474</v>
+      </c>
+      <c r="D10">
+        <v>743.4242305768474</v>
+      </c>
+      <c r="E10">
+        <v>38.592</v>
+      </c>
+      <c r="F10">
+        <v>58.592</v>
+      </c>
+      <c r="G10">
+        <v>20.3</v>
+      </c>
+      <c r="H10">
+        <v>712.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>13.1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>12.1</v>
+      </c>
+      <c r="M10">
+        <v>3.2928704</v>
+      </c>
+      <c r="N10">
+        <v>8.8071296</v>
+      </c>
+      <c r="O10">
+        <v>3.08249536</v>
+      </c>
+      <c r="P10">
+        <v>5.72463424</v>
+      </c>
+      <c r="Q10">
+        <v>6.72463424</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1431120446464548</v>
+      </c>
+      <c r="T10">
+        <v>0.4709305395999149</v>
+      </c>
+      <c r="U10">
+        <v>0.0562</v>
+      </c>
+      <c r="V10">
+        <v>0.35</v>
+      </c>
+      <c r="W10">
+        <v>0.03653</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>3.674605596381807</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1344921705976174</v>
+      </c>
+      <c r="C11">
+        <v>698.5331516359602</v>
+      </c>
+      <c r="D11">
+        <v>744.1491516359603</v>
+      </c>
+      <c r="E11">
+        <v>45.916</v>
+      </c>
+      <c r="F11">
+        <v>65.916</v>
+      </c>
+      <c r="G11">
+        <v>20.3</v>
+      </c>
+      <c r="H11">
+        <v>712.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>13.1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>12.1</v>
+      </c>
+      <c r="M11">
+        <v>4.0142844</v>
+      </c>
+      <c r="N11">
+        <v>8.0857156</v>
+      </c>
+      <c r="O11">
+        <v>2.83000046</v>
+      </c>
+      <c r="P11">
+        <v>5.25571514</v>
+      </c>
+      <c r="Q11">
+        <v>6.25571514</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1438785940633159</v>
+      </c>
+      <c r="T11">
+        <v>0.4743912284564692</v>
+      </c>
+      <c r="U11">
+        <v>0.0609</v>
+      </c>
+      <c r="V11">
+        <v>0.35</v>
+      </c>
+      <c r="W11">
+        <v>0.039585</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>3.014235862312097</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1350644601204965</v>
+      </c>
+      <c r="C12">
+        <v>686.7852057434935</v>
+      </c>
+      <c r="D12">
+        <v>739.7252057434936</v>
+      </c>
+      <c r="E12">
+        <v>53.23999999999999</v>
+      </c>
+      <c r="F12">
+        <v>73.23999999999999</v>
+      </c>
+      <c r="G12">
+        <v>20.3</v>
+      </c>
+      <c r="H12">
+        <v>712.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>13.1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>12.1</v>
+      </c>
+      <c r="M12">
+        <v>5.485675999999999</v>
+      </c>
+      <c r="N12">
+        <v>6.614324000000001</v>
+      </c>
+      <c r="O12">
+        <v>2.3150134</v>
+      </c>
+      <c r="P12">
+        <v>4.2993106</v>
+      </c>
+      <c r="Q12">
+        <v>5.2993106</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1446621779116628</v>
+      </c>
+      <c r="T12">
+        <v>0.4779288215098359</v>
+      </c>
+      <c r="U12">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V12">
+        <v>0.35</v>
+      </c>
+      <c r="W12">
+        <v>0.048685</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>2.205744560925582</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1348177496433755</v>
+      </c>
+      <c r="C13">
+        <v>681.3618747252726</v>
+      </c>
+      <c r="D13">
+        <v>741.6258747252726</v>
+      </c>
+      <c r="E13">
+        <v>60.56399999999999</v>
+      </c>
+      <c r="F13">
+        <v>80.56399999999999</v>
+      </c>
+      <c r="G13">
+        <v>20.3</v>
+      </c>
+      <c r="H13">
+        <v>712.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>13.1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>12.1</v>
+      </c>
+      <c r="M13">
+        <v>6.034243599999999</v>
+      </c>
+      <c r="N13">
+        <v>6.065756400000001</v>
+      </c>
+      <c r="O13">
+        <v>2.12301474</v>
+      </c>
+      <c r="P13">
+        <v>3.942741660000001</v>
+      </c>
+      <c r="Q13">
+        <v>4.942741660000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1454633703858152</v>
+      </c>
+      <c r="T13">
+        <v>0.4815459110363119</v>
+      </c>
+      <c r="U13">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V13">
+        <v>0.35</v>
+      </c>
+      <c r="W13">
+        <v>0.048685</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>2.005222328114165</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1358424391662546</v>
+      </c>
+      <c r="C14">
+        <v>666.2069064370057</v>
+      </c>
+      <c r="D14">
+        <v>733.7949064370058</v>
+      </c>
+      <c r="E14">
+        <v>67.88799999999999</v>
+      </c>
+      <c r="F14">
+        <v>87.88799999999999</v>
+      </c>
+      <c r="G14">
+        <v>20.3</v>
+      </c>
+      <c r="H14">
+        <v>712.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>13.1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>12.1</v>
+      </c>
+      <c r="M14">
+        <v>8.0153856</v>
+      </c>
+      <c r="N14">
+        <v>4.0846144</v>
+      </c>
+      <c r="O14">
+        <v>1.42961504</v>
+      </c>
+      <c r="P14">
+        <v>2.65499936</v>
+      </c>
+      <c r="Q14">
+        <v>3.65499936</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1462827717798347</v>
+      </c>
+      <c r="T14">
+        <v>0.4852452071429351</v>
+      </c>
+      <c r="U14">
+        <v>0.0912</v>
+      </c>
+      <c r="V14">
+        <v>0.35</v>
+      </c>
+      <c r="W14">
+        <v>0.05928000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>1.509596743542818</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1434176027856648</v>
+      </c>
+      <c r="C15">
+        <v>605.750199021234</v>
+      </c>
+      <c r="D15">
+        <v>680.6621990212341</v>
+      </c>
+      <c r="E15">
+        <v>75.212</v>
+      </c>
+      <c r="F15">
+        <v>95.212</v>
+      </c>
+      <c r="G15">
+        <v>20.3</v>
+      </c>
+      <c r="H15">
+        <v>712.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>13.1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>12.1</v>
+      </c>
+      <c r="M15">
+        <v>14.9101992</v>
+      </c>
+      <c r="N15">
+        <v>-2.810199200000003</v>
+      </c>
+      <c r="O15">
+        <v>-0.983569720000001</v>
+      </c>
+      <c r="P15">
+        <v>-1.826629480000002</v>
+      </c>
+      <c r="Q15">
+        <v>-0.826629480000002</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1480942093702658</v>
+      </c>
+      <c r="T15">
+        <v>0.4934231820336062</v>
+      </c>
+      <c r="U15">
+        <v>0.1566</v>
+      </c>
+      <c r="V15">
+        <v>0.2840337639486398</v>
+      </c>
+      <c r="W15">
+        <v>0.112120312565643</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.8115250398532567</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1528150034705585</v>
+      </c>
+      <c r="C16">
+        <v>542.3243245261363</v>
+      </c>
+      <c r="D16">
+        <v>624.5603245261364</v>
+      </c>
+      <c r="E16">
+        <v>82.536</v>
+      </c>
+      <c r="F16">
+        <v>102.536</v>
+      </c>
+      <c r="G16">
+        <v>20.3</v>
+      </c>
+      <c r="H16">
+        <v>712.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>13.1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>12.1</v>
+      </c>
+      <c r="M16">
+        <v>21.4095168</v>
+      </c>
+      <c r="N16">
+        <v>-9.309516800000003</v>
+      </c>
+      <c r="O16">
+        <v>-3.258330880000001</v>
+      </c>
+      <c r="P16">
+        <v>-6.051185920000002</v>
+      </c>
+      <c r="Q16">
+        <v>-5.051185920000002</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1504248405081686</v>
+      </c>
+      <c r="T16">
+        <v>0.5039451249511371</v>
+      </c>
+      <c r="U16">
+        <v>0.2088</v>
+      </c>
+      <c r="V16">
+        <v>0.1978092284642313</v>
+      </c>
+      <c r="W16">
+        <v>0.1674974330966685</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.5651692241835182</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1545150034705585</v>
+      </c>
+      <c r="C17">
+        <v>525.8247421051016</v>
+      </c>
+      <c r="D17">
+        <v>615.3847421051016</v>
+      </c>
+      <c r="E17">
+        <v>89.86</v>
+      </c>
+      <c r="F17">
+        <v>109.86</v>
+      </c>
+      <c r="G17">
+        <v>20.3</v>
+      </c>
+      <c r="H17">
+        <v>712.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>13.1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>12.1</v>
+      </c>
+      <c r="M17">
+        <v>22.938768</v>
+      </c>
+      <c r="N17">
+        <v>-10.838768</v>
+      </c>
+      <c r="O17">
+        <v>-3.7935688</v>
+      </c>
+      <c r="P17">
+        <v>-7.045199200000001</v>
+      </c>
+      <c r="Q17">
+        <v>-6.045199200000001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1517380739259117</v>
+      </c>
+      <c r="T17">
+        <v>0.5098738911270327</v>
+      </c>
+      <c r="U17">
+        <v>0.2088</v>
+      </c>
+      <c r="V17">
+        <v>0.1846219465666159</v>
+      </c>
+      <c r="W17">
+        <v>0.1702509375568906</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.5274912759046171</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1613584961909959</v>
+      </c>
+      <c r="C18">
+        <v>484.1385303144033</v>
+      </c>
+      <c r="D18">
+        <v>581.0225303144033</v>
+      </c>
+      <c r="E18">
+        <v>97.184</v>
+      </c>
+      <c r="F18">
+        <v>117.184</v>
+      </c>
+      <c r="G18">
+        <v>20.3</v>
+      </c>
+      <c r="H18">
+        <v>712.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>13.1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>12.1</v>
+      </c>
+      <c r="M18">
+        <v>27.9835392</v>
+      </c>
+      <c r="N18">
+        <v>-15.8835392</v>
+      </c>
+      <c r="O18">
+        <v>-5.55923872</v>
+      </c>
+      <c r="P18">
+        <v>-10.32430048</v>
+      </c>
+      <c r="Q18">
+        <v>-9.32430048</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1534914947112647</v>
+      </c>
+      <c r="T18">
+        <v>0.5177899414680135</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.1513389700184886</v>
+      </c>
+      <c r="W18">
+        <v>0.2026602539595849</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.4323970571956817</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1633584961909959</v>
+      </c>
+      <c r="C19">
+        <v>467.4852184154627</v>
+      </c>
+      <c r="D19">
+        <v>571.6932184154628</v>
+      </c>
+      <c r="E19">
+        <v>104.508</v>
+      </c>
+      <c r="F19">
+        <v>124.508</v>
+      </c>
+      <c r="G19">
+        <v>20.3</v>
+      </c>
+      <c r="H19">
+        <v>712.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>13.1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>12.1</v>
+      </c>
+      <c r="M19">
+        <v>29.7325104</v>
+      </c>
+      <c r="N19">
+        <v>-17.6325104</v>
+      </c>
+      <c r="O19">
+        <v>-6.17137864</v>
+      </c>
+      <c r="P19">
+        <v>-11.46113176</v>
+      </c>
+      <c r="Q19">
+        <v>-10.46113176</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1548733199487498</v>
+      </c>
+      <c r="T19">
+        <v>0.5240283744977486</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.1424366776644598</v>
+      </c>
+      <c r="W19">
+        <v>0.204786121373727</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.406961936184171</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1653584961909959</v>
+      </c>
+      <c r="C20">
+        <v>451.1267681711631</v>
+      </c>
+      <c r="D20">
+        <v>562.6587681711632</v>
+      </c>
+      <c r="E20">
+        <v>111.832</v>
+      </c>
+      <c r="F20">
+        <v>131.832</v>
+      </c>
+      <c r="G20">
+        <v>20.3</v>
+      </c>
+      <c r="H20">
+        <v>712.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>13.1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>12.1</v>
+      </c>
+      <c r="M20">
+        <v>31.4814816</v>
+      </c>
+      <c r="N20">
+        <v>-19.3814816</v>
+      </c>
+      <c r="O20">
+        <v>-6.78351856</v>
+      </c>
+      <c r="P20">
+        <v>-12.59796304</v>
+      </c>
+      <c r="Q20">
+        <v>-11.59796304</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1562888482408077</v>
+      </c>
+      <c r="T20">
+        <v>0.530418964430648</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.1345235289053232</v>
+      </c>
+      <c r="W20">
+        <v>0.2066757812974089</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.3843529397294948</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1673584961909959</v>
+      </c>
+      <c r="C21">
+        <v>435.0494179867421</v>
+      </c>
+      <c r="D21">
+        <v>553.9054179867421</v>
+      </c>
+      <c r="E21">
+        <v>119.156</v>
+      </c>
+      <c r="F21">
+        <v>139.156</v>
+      </c>
+      <c r="G21">
+        <v>20.3</v>
+      </c>
+      <c r="H21">
+        <v>712.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>13.1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>12.1</v>
+      </c>
+      <c r="M21">
+        <v>33.2304528</v>
+      </c>
+      <c r="N21">
+        <v>-21.1304528</v>
+      </c>
+      <c r="O21">
+        <v>-7.39565848</v>
+      </c>
+      <c r="P21">
+        <v>-13.73479432</v>
+      </c>
+      <c r="Q21">
+        <v>-12.73479432</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1577393278487189</v>
+      </c>
+      <c r="T21">
+        <v>0.5369673467075695</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.127443343173464</v>
+      </c>
+      <c r="W21">
+        <v>0.2083665296501768</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.3641238376384688</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1693584961909959</v>
+      </c>
+      <c r="C22">
+        <v>419.2402495121233</v>
+      </c>
+      <c r="D22">
+        <v>545.4202495121234</v>
+      </c>
+      <c r="E22">
+        <v>126.48</v>
+      </c>
+      <c r="F22">
+        <v>146.48</v>
+      </c>
+      <c r="G22">
+        <v>20.3</v>
+      </c>
+      <c r="H22">
+        <v>712.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>13.1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>12.1</v>
+      </c>
+      <c r="M22">
+        <v>34.979424</v>
+      </c>
+      <c r="N22">
+        <v>-22.879424</v>
+      </c>
+      <c r="O22">
+        <v>-8.0077984</v>
+      </c>
+      <c r="P22">
+        <v>-14.8716256</v>
+      </c>
+      <c r="Q22">
+        <v>-13.8716256</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1592260694468279</v>
+      </c>
+      <c r="T22">
+        <v>0.5436794385414141</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.1210711760147909</v>
+      </c>
+      <c r="W22">
+        <v>0.209888203167668</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.3459176457565454</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1713584961909959</v>
+      </c>
+      <c r="C23">
+        <v>403.6871240288913</v>
+      </c>
+      <c r="D23">
+        <v>537.1911240288913</v>
+      </c>
+      <c r="E23">
+        <v>133.804</v>
+      </c>
+      <c r="F23">
+        <v>153.804</v>
+      </c>
+      <c r="G23">
+        <v>20.3</v>
+      </c>
+      <c r="H23">
+        <v>712.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>13.1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>12.1</v>
+      </c>
+      <c r="M23">
+        <v>36.7283952</v>
+      </c>
+      <c r="N23">
+        <v>-24.6283952</v>
+      </c>
+      <c r="O23">
+        <v>-8.619938319999999</v>
+      </c>
+      <c r="P23">
+        <v>-16.00845688</v>
+      </c>
+      <c r="Q23">
+        <v>-15.00845688</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1607504500727371</v>
+      </c>
+      <c r="T23">
+        <v>0.5505614567507991</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.1153058819188484</v>
+      </c>
+      <c r="W23">
+        <v>0.211264955397779</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.3294453769109956</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1733584961909959</v>
+      </c>
+      <c r="C24">
+        <v>388.3786245103121</v>
+      </c>
+      <c r="D24">
+        <v>529.2066245103122</v>
+      </c>
+      <c r="E24">
+        <v>141.128</v>
+      </c>
+      <c r="F24">
+        <v>161.128</v>
+      </c>
+      <c r="G24">
+        <v>20.3</v>
+      </c>
+      <c r="H24">
+        <v>712.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>13.1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>12.1</v>
+      </c>
+      <c r="M24">
+        <v>38.4773664</v>
+      </c>
+      <c r="N24">
+        <v>-26.3773664</v>
+      </c>
+      <c r="O24">
+        <v>-9.23207824</v>
+      </c>
+      <c r="P24">
+        <v>-17.14528816</v>
+      </c>
+      <c r="Q24">
+        <v>-16.14528816</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1623139173813619</v>
+      </c>
+      <c r="T24">
+        <v>0.5576199369655529</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.1100647054679917</v>
+      </c>
+      <c r="W24">
+        <v>0.2125165483342436</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.3144705870514048</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1753584961909959</v>
+      </c>
+      <c r="C25">
+        <v>373.3040027727944</v>
+      </c>
+      <c r="D25">
+        <v>521.4560027727945</v>
+      </c>
+      <c r="E25">
+        <v>148.452</v>
+      </c>
+      <c r="F25">
+        <v>168.452</v>
+      </c>
+      <c r="G25">
+        <v>20.3</v>
+      </c>
+      <c r="H25">
+        <v>712.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>13.1</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>12.1</v>
+      </c>
+      <c r="M25">
+        <v>40.2263376</v>
+      </c>
+      <c r="N25">
+        <v>-28.1263376</v>
+      </c>
+      <c r="O25">
+        <v>-9.844218159999999</v>
+      </c>
+      <c r="P25">
+        <v>-18.28211944</v>
+      </c>
+      <c r="Q25">
+        <v>-17.28211944</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1639179942304705</v>
+      </c>
+      <c r="T25">
+        <v>0.564861754328742</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.1052792834911225</v>
+      </c>
+      <c r="W25">
+        <v>0.21365930710232</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3007979528317786</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1773584961909959</v>
+      </c>
+      <c r="C26">
+        <v>358.4531312043561</v>
+      </c>
+      <c r="D26">
+        <v>513.9291312043561</v>
+      </c>
+      <c r="E26">
+        <v>155.776</v>
+      </c>
+      <c r="F26">
+        <v>175.776</v>
+      </c>
+      <c r="G26">
+        <v>20.3</v>
+      </c>
+      <c r="H26">
+        <v>712.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>13.1</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>12.1</v>
+      </c>
+      <c r="M26">
+        <v>41.9753088</v>
+      </c>
+      <c r="N26">
+        <v>-29.8753088</v>
+      </c>
+      <c r="O26">
+        <v>-10.45635808</v>
+      </c>
+      <c r="P26">
+        <v>-19.41895072</v>
+      </c>
+      <c r="Q26">
+        <v>-18.41895072</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1655642836282399</v>
+      </c>
+      <c r="T26">
+        <v>0.5722941458330675</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.1008926466789924</v>
+      </c>
+      <c r="W26">
+        <v>0.2147068359730566</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.2882647047971212</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1793584961909959</v>
+      </c>
+      <c r="C27">
+        <v>343.8164586142054</v>
+      </c>
+      <c r="D27">
+        <v>506.6164586142054</v>
+      </c>
+      <c r="E27">
+        <v>163.1</v>
+      </c>
+      <c r="F27">
+        <v>183.1</v>
+      </c>
+      <c r="G27">
+        <v>20.3</v>
+      </c>
+      <c r="H27">
+        <v>712.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>13.1</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>12.1</v>
+      </c>
+      <c r="M27">
+        <v>43.72428</v>
+      </c>
+      <c r="N27">
+        <v>-31.62428</v>
+      </c>
+      <c r="O27">
+        <v>-11.068498</v>
+      </c>
+      <c r="P27">
+        <v>-20.555782</v>
+      </c>
+      <c r="Q27">
+        <v>-19.555782</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1672544740766164</v>
+      </c>
+      <c r="T27">
+        <v>0.579924734444175</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.09685694081183269</v>
+      </c>
+      <c r="W27">
+        <v>0.2156705625341344</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.2767341166052363</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1813584961909959</v>
+      </c>
+      <c r="C28">
+        <v>329.3849697987304</v>
+      </c>
+      <c r="D28">
+        <v>499.5089697987304</v>
+      </c>
+      <c r="E28">
+        <v>170.424</v>
+      </c>
+      <c r="F28">
+        <v>190.424</v>
+      </c>
+      <c r="G28">
+        <v>20.3</v>
+      </c>
+      <c r="H28">
+        <v>712.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>13.1</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>12.1</v>
+      </c>
+      <c r="M28">
+        <v>45.47325120000001</v>
+      </c>
+      <c r="N28">
+        <v>-33.37325120000001</v>
+      </c>
+      <c r="O28">
+        <v>-11.68063792</v>
+      </c>
+      <c r="P28">
+        <v>-21.69261328</v>
+      </c>
+      <c r="Q28">
+        <v>-20.69261328</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1689903453479221</v>
+      </c>
+      <c r="T28">
+        <v>0.5877615551799072</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.09313167385753141</v>
+      </c>
+      <c r="W28">
+        <v>0.2165601562828215</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.2660904967358041</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1833584961909959</v>
+      </c>
+      <c r="C29">
+        <v>315.150148463971</v>
+      </c>
+      <c r="D29">
+        <v>492.5981484639711</v>
+      </c>
+      <c r="E29">
+        <v>177.748</v>
+      </c>
+      <c r="F29">
+        <v>197.748</v>
+      </c>
+      <c r="G29">
+        <v>20.3</v>
+      </c>
+      <c r="H29">
+        <v>712.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>13.1</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>12.1</v>
+      </c>
+      <c r="M29">
+        <v>47.22222240000001</v>
+      </c>
+      <c r="N29">
+        <v>-35.12222240000001</v>
+      </c>
+      <c r="O29">
+        <v>-12.29277784</v>
+      </c>
+      <c r="P29">
+        <v>-22.82944456000001</v>
+      </c>
+      <c r="Q29">
+        <v>-21.82944456000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1707737747362497</v>
+      </c>
+      <c r="T29">
+        <v>0.5958130833330566</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.08968235260354876</v>
+      </c>
+      <c r="W29">
+        <v>0.2173838541982726</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.2562352931529965</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1853584961909959</v>
+      </c>
+      <c r="C30">
+        <v>301.103943183944</v>
+      </c>
+      <c r="D30">
+        <v>485.8759431839439</v>
+      </c>
+      <c r="E30">
+        <v>185.072</v>
+      </c>
+      <c r="F30">
+        <v>205.072</v>
+      </c>
+      <c r="G30">
+        <v>20.3</v>
+      </c>
+      <c r="H30">
+        <v>712.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>13.1</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>12.1</v>
+      </c>
+      <c r="M30">
+        <v>48.97119360000001</v>
+      </c>
+      <c r="N30">
+        <v>-36.87119360000001</v>
+      </c>
+      <c r="O30">
+        <v>-12.90491776</v>
+      </c>
+      <c r="P30">
+        <v>-23.96627584</v>
+      </c>
+      <c r="Q30">
+        <v>-22.96627584</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1726067438298088</v>
+      </c>
+      <c r="T30">
+        <v>0.6040882650460158</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.08647941143913632</v>
+      </c>
+      <c r="W30">
+        <v>0.2181487165483343</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.2470840326832466</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1873584961909959</v>
+      </c>
+      <c r="C31">
+        <v>287.2387361087289</v>
+      </c>
+      <c r="D31">
+        <v>479.3347361087288</v>
+      </c>
+      <c r="E31">
+        <v>192.396</v>
+      </c>
+      <c r="F31">
+        <v>212.396</v>
+      </c>
+      <c r="G31">
+        <v>20.3</v>
+      </c>
+      <c r="H31">
+        <v>712.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>13.1</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
+        <v>12.1</v>
+      </c>
+      <c r="M31">
+        <v>50.7201648</v>
+      </c>
+      <c r="N31">
+        <v>-38.6201648</v>
+      </c>
+      <c r="O31">
+        <v>-13.51705768</v>
+      </c>
+      <c r="P31">
+        <v>-25.10310712</v>
+      </c>
+      <c r="Q31">
+        <v>-24.10310712</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1744913458555807</v>
+      </c>
+      <c r="T31">
+        <v>0.612596550469199</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.08349736276882128</v>
+      </c>
+      <c r="W31">
+        <v>0.2188608297708055</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2385638936252037</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1893584961909959</v>
+      </c>
+      <c r="C32">
+        <v>273.54731416662</v>
+      </c>
+      <c r="D32">
+        <v>472.96731416662</v>
+      </c>
+      <c r="E32">
+        <v>199.72</v>
+      </c>
+      <c r="F32">
+        <v>219.72</v>
+      </c>
+      <c r="G32">
+        <v>20.3</v>
+      </c>
+      <c r="H32">
+        <v>712.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>13.1</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>12.1</v>
+      </c>
+      <c r="M32">
+        <v>52.469136</v>
+      </c>
+      <c r="N32">
+        <v>-40.369136</v>
+      </c>
+      <c r="O32">
+        <v>-14.1291976</v>
+      </c>
+      <c r="P32">
+        <v>-26.2399384</v>
+      </c>
+      <c r="Q32">
+        <v>-25.2399384</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1764297936535176</v>
+      </c>
+      <c r="T32">
+        <v>0.6213479297616161</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.08071411734319391</v>
+      </c>
+      <c r="W32">
+        <v>0.2195254687784453</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2306117638376969</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1913584961909959</v>
+      </c>
+      <c r="C33">
+        <v>260.0228425314711</v>
+      </c>
+      <c r="D33">
+        <v>466.7668425314711</v>
+      </c>
+      <c r="E33">
+        <v>207.044</v>
+      </c>
+      <c r="F33">
+        <v>227.044</v>
+      </c>
+      <c r="G33">
+        <v>20.3</v>
+      </c>
+      <c r="H33">
+        <v>712.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>13.1</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>12.1</v>
+      </c>
+      <c r="M33">
+        <v>54.2181072</v>
+      </c>
+      <c r="N33">
+        <v>-42.1181072</v>
+      </c>
+      <c r="O33">
+        <v>-14.74133752</v>
+      </c>
+      <c r="P33">
+        <v>-27.37676968</v>
+      </c>
+      <c r="Q33">
+        <v>-26.37676968</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1784244283441483</v>
+      </c>
+      <c r="T33">
+        <v>0.6303529722219294</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.07811043613857474</v>
+      </c>
+      <c r="W33">
+        <v>0.2201472278501084</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2231726746816421</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1933584961909959</v>
+      </c>
+      <c r="C34">
+        <v>246.658840150047</v>
+      </c>
+      <c r="D34">
+        <v>460.726840150047</v>
+      </c>
+      <c r="E34">
+        <v>214.368</v>
+      </c>
+      <c r="F34">
+        <v>234.368</v>
+      </c>
+      <c r="G34">
+        <v>20.3</v>
+      </c>
+      <c r="H34">
+        <v>712.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>13.1</v>
+      </c>
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>12.1</v>
+      </c>
+      <c r="M34">
+        <v>55.9670784</v>
+      </c>
+      <c r="N34">
+        <v>-43.8670784</v>
+      </c>
+      <c r="O34">
+        <v>-15.35347744</v>
+      </c>
+      <c r="P34">
+        <v>-28.51360096</v>
+      </c>
+      <c r="Q34">
+        <v>-27.51360096</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.180477728760974</v>
+      </c>
+      <c r="T34">
+        <v>0.6396228688722519</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.07566948500924428</v>
+      </c>
+      <c r="W34">
+        <v>0.2207301269797925</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2161985285978408</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1953584961909959</v>
+      </c>
+      <c r="C35">
+        <v>233.4491571451723</v>
+      </c>
+      <c r="D35">
+        <v>454.8411571451722</v>
+      </c>
+      <c r="E35">
+        <v>221.692</v>
+      </c>
+      <c r="F35">
+        <v>241.692</v>
+      </c>
+      <c r="G35">
+        <v>20.3</v>
+      </c>
+      <c r="H35">
+        <v>712.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>13.1</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35">
+        <v>12.1</v>
+      </c>
+      <c r="M35">
+        <v>57.71604960000001</v>
+      </c>
+      <c r="N35">
+        <v>-45.6160496</v>
+      </c>
+      <c r="O35">
+        <v>-15.96561736</v>
+      </c>
+      <c r="P35">
+        <v>-29.65043224</v>
+      </c>
+      <c r="Q35">
+        <v>-28.65043224</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1825923217275557</v>
+      </c>
+      <c r="T35">
+        <v>0.6491694788554199</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.07337647031199444</v>
+      </c>
+      <c r="W35">
+        <v>0.2212776988894957</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2096470580342699</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1973584961909959</v>
+      </c>
+      <c r="C36">
+        <v>220.3879539290509</v>
+      </c>
+      <c r="D36">
+        <v>449.1039539290509</v>
+      </c>
+      <c r="E36">
+        <v>229.016</v>
+      </c>
+      <c r="F36">
+        <v>249.016</v>
+      </c>
+      <c r="G36">
+        <v>20.3</v>
+      </c>
+      <c r="H36">
+        <v>712.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>13.1</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>12.1</v>
+      </c>
+      <c r="M36">
+        <v>59.4650208</v>
+      </c>
+      <c r="N36">
+        <v>-47.3650208</v>
+      </c>
+      <c r="O36">
+        <v>-16.57775728</v>
+      </c>
+      <c r="P36">
+        <v>-30.78726352</v>
+      </c>
+      <c r="Q36">
+        <v>-29.78726352</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1847709932688823</v>
+      </c>
+      <c r="T36">
+        <v>0.6590053800501989</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.0712183388322299</v>
+      </c>
+      <c r="W36">
+        <v>0.2217930606868635</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2034809680920855</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1993584961909959</v>
+      </c>
+      <c r="C37">
+        <v>207.4696818776383</v>
+      </c>
+      <c r="D37">
+        <v>443.5096818776383</v>
+      </c>
+      <c r="E37">
+        <v>236.34</v>
+      </c>
+      <c r="F37">
+        <v>256.34</v>
+      </c>
+      <c r="G37">
+        <v>20.3</v>
+      </c>
+      <c r="H37">
+        <v>712.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>13.1</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>12.1</v>
+      </c>
+      <c r="M37">
+        <v>61.21399200000001</v>
+      </c>
+      <c r="N37">
+        <v>-49.11399200000001</v>
+      </c>
+      <c r="O37">
+        <v>-17.1898972</v>
+      </c>
+      <c r="P37">
+        <v>-31.92409480000001</v>
+      </c>
+      <c r="Q37">
+        <v>-30.92409480000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1870167008576343</v>
+      </c>
+      <c r="T37">
+        <v>0.6691439243586637</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.06918352915130904</v>
+      </c>
+      <c r="W37">
+        <v>0.2222789732386674</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.1976672261465973</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2013584961909959</v>
+      </c>
+      <c r="C38">
+        <v>194.6890654316233</v>
+      </c>
+      <c r="D38">
+        <v>438.0530654316233</v>
+      </c>
+      <c r="E38">
+        <v>243.664</v>
+      </c>
+      <c r="F38">
+        <v>263.664</v>
+      </c>
+      <c r="G38">
+        <v>20.3</v>
+      </c>
+      <c r="H38">
+        <v>712.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>13.1</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
+        <v>12.1</v>
+      </c>
+      <c r="M38">
+        <v>62.9629632</v>
+      </c>
+      <c r="N38">
+        <v>-50.8629632</v>
+      </c>
+      <c r="O38">
+        <v>-17.80203712</v>
+      </c>
+      <c r="P38">
+        <v>-33.06092608</v>
+      </c>
+      <c r="Q38">
+        <v>-32.06092608</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1893325868085348</v>
+      </c>
+      <c r="T38">
+        <v>0.6795992981767677</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.06726176445266159</v>
+      </c>
+      <c r="W38">
+        <v>0.2227378906487044</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.1921764698647475</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2033584961909959</v>
+      </c>
+      <c r="C39">
+        <v>182.0410855026478</v>
+      </c>
+      <c r="D39">
+        <v>432.7290855026478</v>
+      </c>
+      <c r="E39">
+        <v>250.988</v>
+      </c>
+      <c r="F39">
+        <v>270.988</v>
+      </c>
+      <c r="G39">
+        <v>20.3</v>
+      </c>
+      <c r="H39">
+        <v>712.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>13.1</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>12.1</v>
+      </c>
+      <c r="M39">
+        <v>64.7119344</v>
+      </c>
+      <c r="N39">
+        <v>-52.6119344</v>
+      </c>
+      <c r="O39">
+        <v>-18.41417704</v>
+      </c>
+      <c r="P39">
+        <v>-34.19775736</v>
+      </c>
+      <c r="Q39">
+        <v>-33.19775736</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1917219929483529</v>
+      </c>
+      <c r="T39">
+        <v>0.690386588624018</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.06544387892691397</v>
+      </c>
+      <c r="W39">
+        <v>0.223172001712253</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.1869825112197543</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2053584961909959</v>
+      </c>
+      <c r="C40">
+        <v>169.5209640750572</v>
+      </c>
+      <c r="D40">
+        <v>427.5329640750572</v>
+      </c>
+      <c r="E40">
+        <v>258.312</v>
+      </c>
+      <c r="F40">
+        <v>278.312</v>
+      </c>
+      <c r="G40">
+        <v>20.3</v>
+      </c>
+      <c r="H40">
+        <v>712.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>13.1</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <v>12.1</v>
+      </c>
+      <c r="M40">
+        <v>66.4609056</v>
+      </c>
+      <c r="N40">
+        <v>-54.3609056</v>
+      </c>
+      <c r="O40">
+        <v>-19.02631696</v>
+      </c>
+      <c r="P40">
+        <v>-35.33458864000001</v>
+      </c>
+      <c r="Q40">
+        <v>-34.33458864000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1941884767055843</v>
+      </c>
+      <c r="T40">
+        <v>0.7015218561824698</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.06372167158673202</v>
+      </c>
+      <c r="W40">
+        <v>0.2235832648250884</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.1820619188192344</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2073584961909959</v>
+      </c>
+      <c r="C41">
+        <v>157.1241499038794</v>
+      </c>
+      <c r="D41">
+        <v>422.4601499038794</v>
+      </c>
+      <c r="E41">
+        <v>265.636</v>
+      </c>
+      <c r="F41">
+        <v>285.636</v>
+      </c>
+      <c r="G41">
+        <v>20.3</v>
+      </c>
+      <c r="H41">
+        <v>712.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>13.1</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>12.1</v>
+      </c>
+      <c r="M41">
+        <v>68.2098768</v>
+      </c>
+      <c r="N41">
+        <v>-56.1098768</v>
+      </c>
+      <c r="O41">
+        <v>-19.63845688</v>
+      </c>
+      <c r="P41">
+        <v>-36.47141992</v>
+      </c>
+      <c r="Q41">
+        <v>-35.47141992</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1967358287827251</v>
+      </c>
+      <c r="T41">
+        <v>0.713022214480543</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.06208778257168761</v>
+      </c>
+      <c r="W41">
+        <v>0.223973437521881</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.1773936644905361</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2093584961909959</v>
+      </c>
+      <c r="C42">
+        <v>144.846305219053</v>
+      </c>
+      <c r="D42">
+        <v>417.5063052190529</v>
+      </c>
+      <c r="E42">
+        <v>272.96</v>
+      </c>
+      <c r="F42">
+        <v>292.96</v>
+      </c>
+      <c r="G42">
+        <v>20.3</v>
+      </c>
+      <c r="H42">
+        <v>712.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>13.1</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>12.1</v>
+      </c>
+      <c r="M42">
+        <v>69.958848</v>
+      </c>
+      <c r="N42">
+        <v>-57.858848</v>
+      </c>
+      <c r="O42">
+        <v>-20.2505968</v>
+      </c>
+      <c r="P42">
+        <v>-37.6082512</v>
+      </c>
+      <c r="Q42">
+        <v>-36.6082512</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1993680925957705</v>
+      </c>
+      <c r="T42">
+        <v>0.7249059180552189</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.06053558800739543</v>
+      </c>
+      <c r="W42">
+        <v>0.224344101583834</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.1729588228782727</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2113584961909959</v>
+      </c>
+      <c r="C43">
+        <v>132.6832933542656</v>
+      </c>
+      <c r="D43">
+        <v>412.6672933542656</v>
+      </c>
+      <c r="E43">
+        <v>280.284</v>
+      </c>
+      <c r="F43">
+        <v>300.284</v>
+      </c>
+      <c r="G43">
+        <v>20.3</v>
+      </c>
+      <c r="H43">
+        <v>712.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>13.1</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>12.1</v>
+      </c>
+      <c r="M43">
+        <v>71.7078192</v>
+      </c>
+      <c r="N43">
+        <v>-59.6078192</v>
+      </c>
+      <c r="O43">
+        <v>-20.86273672</v>
+      </c>
+      <c r="P43">
+        <v>-38.74508248</v>
+      </c>
+      <c r="Q43">
+        <v>-37.74508248</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2020895856906141</v>
+      </c>
+      <c r="T43">
+        <v>0.7371924590392055</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.05905911025111749</v>
+      </c>
+      <c r="W43">
+        <v>0.2246966844720331</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.1687403150031929</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2133584961909959</v>
+      </c>
+      <c r="C44">
+        <v>120.6311672262454</v>
+      </c>
+      <c r="D44">
+        <v>407.9391672262454</v>
+      </c>
+      <c r="E44">
+        <v>287.608</v>
+      </c>
+      <c r="F44">
+        <v>307.608</v>
+      </c>
+      <c r="G44">
+        <v>20.3</v>
+      </c>
+      <c r="H44">
+        <v>712.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>13.1</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44">
+        <v>12.1</v>
+      </c>
+      <c r="M44">
+        <v>73.4567904</v>
+      </c>
+      <c r="N44">
+        <v>-61.3567904</v>
+      </c>
+      <c r="O44">
+        <v>-21.47487664</v>
+      </c>
+      <c r="P44">
+        <v>-39.88191376</v>
+      </c>
+      <c r="Q44">
+        <v>-38.88191376</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.204904923374935</v>
+      </c>
+      <c r="T44">
+        <v>0.7499026738502264</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.05765294095942421</v>
+      </c>
+      <c r="W44">
+        <v>0.2250324776988895</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1647226884554978</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2153584961909959</v>
+      </c>
+      <c r="C45">
+        <v>108.6861585970719</v>
+      </c>
+      <c r="D45">
+        <v>403.3181585970718</v>
+      </c>
+      <c r="E45">
+        <v>294.932</v>
+      </c>
+      <c r="F45">
+        <v>314.932</v>
+      </c>
+      <c r="G45">
+        <v>20.3</v>
+      </c>
+      <c r="H45">
+        <v>712.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>13.1</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>12.1</v>
+      </c>
+      <c r="M45">
+        <v>75.20576159999999</v>
+      </c>
+      <c r="N45">
+        <v>-63.10576159999999</v>
+      </c>
+      <c r="O45">
+        <v>-22.08701656</v>
+      </c>
+      <c r="P45">
+        <v>-41.01874503999999</v>
+      </c>
+      <c r="Q45">
+        <v>-40.01874503999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2078190448376532</v>
+      </c>
+      <c r="T45">
+        <v>0.7630588611107567</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.05631217489060041</v>
+      </c>
+      <c r="W45">
+        <v>0.2253526526361246</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1608919282588583</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2173584961909959</v>
+      </c>
+      <c r="C46">
+        <v>96.84466805810973</v>
+      </c>
+      <c r="D46">
+        <v>398.8006680581097</v>
+      </c>
+      <c r="E46">
+        <v>302.256</v>
+      </c>
+      <c r="F46">
+        <v>322.256</v>
+      </c>
+      <c r="G46">
+        <v>20.3</v>
+      </c>
+      <c r="H46">
+        <v>712.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>13.1</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <v>12.1</v>
+      </c>
+      <c r="M46">
+        <v>76.9547328</v>
+      </c>
+      <c r="N46">
+        <v>-64.85473280000001</v>
+      </c>
+      <c r="O46">
+        <v>-22.69915648</v>
+      </c>
+      <c r="P46">
+        <v>-42.15557632000001</v>
+      </c>
+      <c r="Q46">
+        <v>-41.15557632000001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.210837242066897</v>
+      </c>
+      <c r="T46">
+        <v>0.7766849122020202</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.05503235273399584</v>
+      </c>
+      <c r="W46">
+        <v>0.2256582741671218</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.1572352935257023</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2193584961909959</v>
+      </c>
+      <c r="C47">
+        <v>85.10325567961655</v>
+      </c>
+      <c r="D47">
+        <v>394.3832556796165</v>
+      </c>
+      <c r="E47">
+        <v>309.58</v>
+      </c>
+      <c r="F47">
+        <v>329.58</v>
+      </c>
+      <c r="G47">
+        <v>20.3</v>
+      </c>
+      <c r="H47">
+        <v>712.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>13.1</v>
+      </c>
+      <c r="K47">
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>12.1</v>
+      </c>
+      <c r="M47">
+        <v>78.703704</v>
+      </c>
+      <c r="N47">
+        <v>-66.60370400000001</v>
+      </c>
+      <c r="O47">
+        <v>-23.3112964</v>
+      </c>
+      <c r="P47">
+        <v>-43.2924076</v>
+      </c>
+      <c r="Q47">
+        <v>-42.2924076</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2139651919226587</v>
+      </c>
+      <c r="T47">
+        <v>0.7908064560602386</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.05380941156212927</v>
+      </c>
+      <c r="W47">
+        <v>0.2259503125189636</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1537411758917978</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2213584961909959</v>
+      </c>
+      <c r="C48">
+        <v>73.45863227497358</v>
+      </c>
+      <c r="D48">
+        <v>390.0626322749736</v>
+      </c>
+      <c r="E48">
+        <v>316.904</v>
+      </c>
+      <c r="F48">
+        <v>336.904</v>
+      </c>
+      <c r="G48">
+        <v>20.3</v>
+      </c>
+      <c r="H48">
+        <v>712.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>13.1</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <v>12.1</v>
+      </c>
+      <c r="M48">
+        <v>80.4526752</v>
+      </c>
+      <c r="N48">
+        <v>-68.35267520000001</v>
+      </c>
+      <c r="O48">
+        <v>-23.92343632</v>
+      </c>
+      <c r="P48">
+        <v>-44.42923888000001</v>
+      </c>
+      <c r="Q48">
+        <v>-43.42923888000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2172089917730783</v>
+      </c>
+      <c r="T48">
+        <v>0.8054510200613543</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.05263964174556124</v>
+      </c>
+      <c r="W48">
+        <v>0.22622965355116</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1503989764158892</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2233584961909959</v>
+      </c>
+      <c r="C49">
+        <v>61.90765123291629</v>
+      </c>
+      <c r="D49">
+        <v>385.8356512329163</v>
+      </c>
+      <c r="E49">
+        <v>324.228</v>
+      </c>
+      <c r="F49">
+        <v>344.228</v>
+      </c>
+      <c r="G49">
+        <v>20.3</v>
+      </c>
+      <c r="H49">
+        <v>712.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>13.1</v>
+      </c>
+      <c r="K49">
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <v>12.1</v>
+      </c>
+      <c r="M49">
+        <v>82.2016464</v>
+      </c>
+      <c r="N49">
+        <v>-70.10164640000001</v>
+      </c>
+      <c r="O49">
+        <v>-24.53557624</v>
+      </c>
+      <c r="P49">
+        <v>-45.56607016000001</v>
+      </c>
+      <c r="Q49">
+        <v>-44.56607016000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2205751991650232</v>
+      </c>
+      <c r="T49">
+        <v>0.8206482091191156</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.05151964936799611</v>
+      </c>
+      <c r="W49">
+        <v>0.2264971077309225</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1471989981942745</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2253584961909959</v>
+      </c>
+      <c r="C50">
+        <v>50.44730087514012</v>
+      </c>
+      <c r="D50">
+        <v>381.6993008751401</v>
+      </c>
+      <c r="E50">
+        <v>331.552</v>
+      </c>
+      <c r="F50">
+        <v>351.552</v>
+      </c>
+      <c r="G50">
+        <v>20.3</v>
+      </c>
+      <c r="H50">
+        <v>712.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>13.1</v>
+      </c>
+      <c r="K50">
+        <v>1</v>
+      </c>
+      <c r="L50">
+        <v>12.1</v>
+      </c>
+      <c r="M50">
+        <v>83.9506176</v>
+      </c>
+      <c r="N50">
+        <v>-71.85061760000001</v>
+      </c>
+      <c r="O50">
+        <v>-25.14771616</v>
+      </c>
+      <c r="P50">
+        <v>-46.70290144000001</v>
+      </c>
+      <c r="Q50">
+        <v>-45.70290144000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2240708760720429</v>
+      </c>
+      <c r="T50">
+        <v>0.8364299054483294</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.05044632333949618</v>
+      </c>
+      <c r="W50">
+        <v>0.2267534179865283</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1441323523985605</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2273584961909959</v>
+      </c>
+      <c r="C51">
+        <v>39.07469730027367</v>
+      </c>
+      <c r="D51">
+        <v>377.6506973002736</v>
+      </c>
+      <c r="E51">
+        <v>338.876</v>
+      </c>
+      <c r="F51">
+        <v>358.876</v>
+      </c>
+      <c r="G51">
+        <v>20.3</v>
+      </c>
+      <c r="H51">
+        <v>712.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>13.1</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51">
+        <v>12.1</v>
+      </c>
+      <c r="M51">
+        <v>85.6995888</v>
+      </c>
+      <c r="N51">
+        <v>-73.59958880000001</v>
+      </c>
+      <c r="O51">
+        <v>-25.75985608</v>
+      </c>
+      <c r="P51">
+        <v>-47.83973272</v>
+      </c>
+      <c r="Q51">
+        <v>-46.83973272</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2277036383479653</v>
+      </c>
+      <c r="T51">
+        <v>0.8528304918296692</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.04941680653664933</v>
+      </c>
+      <c r="W51">
+        <v>0.2269992665990481</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.141190875818998</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
         <v>0.5</v>
       </c>
-      <c r="AH3">
-        <v>0.01130268199233717</v>
-      </c>
-      <c r="AI3">
-        <v>0.01997629930590825</v>
-      </c>
-      <c r="AJ3">
-        <v>0.0004841677156967173</v>
-      </c>
-      <c r="AK3">
-        <v>0.0008629616845012082</v>
-      </c>
-      <c r="AL3">
-        <v>0.075</v>
-      </c>
-      <c r="AM3">
-        <v>-1.375</v>
-      </c>
-      <c r="AN3">
-        <v>-1.18</v>
-      </c>
-      <c r="AO3">
-        <v>-127.2</v>
-      </c>
-      <c r="AP3">
-        <v>-0.05</v>
-      </c>
-      <c r="AQ3">
-        <v>6.938181818181818</v>
+      <c r="B52">
+        <v>0.2293584961909959</v>
+      </c>
+      <c r="C52">
+        <v>27.78707767848829</v>
+      </c>
+      <c r="D52">
+        <v>373.6870776784883</v>
+      </c>
+      <c r="E52">
+        <v>346.2</v>
+      </c>
+      <c r="F52">
+        <v>366.2</v>
+      </c>
+      <c r="G52">
+        <v>20.3</v>
+      </c>
+      <c r="H52">
+        <v>712.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>13.1</v>
+      </c>
+      <c r="K52">
+        <v>1</v>
+      </c>
+      <c r="L52">
+        <v>12.1</v>
+      </c>
+      <c r="M52">
+        <v>87.44856</v>
+      </c>
+      <c r="N52">
+        <v>-75.34856000000001</v>
+      </c>
+      <c r="O52">
+        <v>-26.371996</v>
+      </c>
+      <c r="P52">
+        <v>-48.97656400000001</v>
+      </c>
+      <c r="Q52">
+        <v>-47.97656400000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2314817111149246</v>
+      </c>
+      <c r="T52">
+        <v>0.8698871016662626</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.04842847040591634</v>
+      </c>
+      <c r="W52">
+        <v>0.2272352812670672</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1383670583026181</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2313584961909959</v>
+      </c>
+      <c r="C53">
+        <v>16.58179396397662</v>
+      </c>
+      <c r="D53">
+        <v>369.8057939639766</v>
+      </c>
+      <c r="E53">
+        <v>353.524</v>
+      </c>
+      <c r="F53">
+        <v>373.524</v>
+      </c>
+      <c r="G53">
+        <v>20.3</v>
+      </c>
+      <c r="H53">
+        <v>712.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>13.1</v>
+      </c>
+      <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>12.1</v>
+      </c>
+      <c r="M53">
+        <v>89.1975312</v>
+      </c>
+      <c r="N53">
+        <v>-77.09753120000001</v>
+      </c>
+      <c r="O53">
+        <v>-26.98413592</v>
+      </c>
+      <c r="P53">
+        <v>-50.11339528000001</v>
+      </c>
+      <c r="Q53">
+        <v>-49.11339528000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2354139909335966</v>
+      </c>
+      <c r="T53">
+        <v>0.8876398996594517</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.04747889255481994</v>
+      </c>
+      <c r="W53">
+        <v>0.227462040457909</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.135653978728057</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2333584961909959</v>
+      </c>
+      <c r="C54">
+        <v>5.456306995235423</v>
+      </c>
+      <c r="D54">
+        <v>366.0043069952354</v>
+      </c>
+      <c r="E54">
+        <v>360.848</v>
+      </c>
+      <c r="F54">
+        <v>380.848</v>
+      </c>
+      <c r="G54">
+        <v>20.3</v>
+      </c>
+      <c r="H54">
+        <v>712.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>13.1</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+      <c r="L54">
+        <v>12.1</v>
+      </c>
+      <c r="M54">
+        <v>90.94650240000001</v>
+      </c>
+      <c r="N54">
+        <v>-78.84650240000002</v>
+      </c>
+      <c r="O54">
+        <v>-27.59627584</v>
+      </c>
+      <c r="P54">
+        <v>-51.25022656000002</v>
+      </c>
+      <c r="Q54">
+        <v>-50.25022656000002</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2395101157447132</v>
+      </c>
+      <c r="T54">
+        <v>0.9061323975690236</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.0465658369287657</v>
+      </c>
+      <c r="W54">
+        <v>0.2276800781414108</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.133045248367902</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2353584961909959</v>
+      </c>
+      <c r="C55">
+        <v>-5.591819044471265</v>
+      </c>
+      <c r="D55">
+        <v>362.2801809555287</v>
+      </c>
+      <c r="E55">
+        <v>368.172</v>
+      </c>
+      <c r="F55">
+        <v>388.172</v>
+      </c>
+      <c r="G55">
+        <v>20.3</v>
+      </c>
+      <c r="H55">
+        <v>712.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>13.1</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55">
+        <v>12.1</v>
+      </c>
+      <c r="M55">
+        <v>92.69547360000001</v>
+      </c>
+      <c r="N55">
+        <v>-80.59547360000002</v>
+      </c>
+      <c r="O55">
+        <v>-28.20841576</v>
+      </c>
+      <c r="P55">
+        <v>-52.38705784000001</v>
+      </c>
+      <c r="Q55">
+        <v>-51.38705784000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2437805437392815</v>
+      </c>
+      <c r="T55">
+        <v>0.9254118102832583</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.04568723623199655</v>
+      </c>
+      <c r="W55">
+        <v>0.2278898879877992</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1305349606628472</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2373584961909959</v>
+      </c>
+      <c r="C56">
+        <v>-16.5649218318639</v>
+      </c>
+      <c r="D56">
+        <v>358.6310781681361</v>
+      </c>
+      <c r="E56">
+        <v>375.496</v>
+      </c>
+      <c r="F56">
+        <v>395.496</v>
+      </c>
+      <c r="G56">
+        <v>20.3</v>
+      </c>
+      <c r="H56">
+        <v>712.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>13.1</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>12.1</v>
+      </c>
+      <c r="M56">
+        <v>94.44444480000001</v>
+      </c>
+      <c r="N56">
+        <v>-82.34444480000002</v>
+      </c>
+      <c r="O56">
+        <v>-28.82055568000001</v>
+      </c>
+      <c r="P56">
+        <v>-53.52388912000001</v>
+      </c>
+      <c r="Q56">
+        <v>-52.52388912000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2482366425162224</v>
+      </c>
+      <c r="T56">
+        <v>0.9455294583328943</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.04484117630177438</v>
+      </c>
+      <c r="W56">
+        <v>0.2280919270991363</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1281176465764982</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2393584961909959</v>
+      </c>
+      <c r="C57">
+        <v>-27.46524579698388</v>
+      </c>
+      <c r="D57">
+        <v>355.0547542030161</v>
+      </c>
+      <c r="E57">
+        <v>382.82</v>
+      </c>
+      <c r="F57">
+        <v>402.82</v>
+      </c>
+      <c r="G57">
+        <v>20.3</v>
+      </c>
+      <c r="H57">
+        <v>712.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>13.1</v>
+      </c>
+      <c r="K57">
+        <v>1</v>
+      </c>
+      <c r="L57">
+        <v>12.1</v>
+      </c>
+      <c r="M57">
+        <v>96.193416</v>
+      </c>
+      <c r="N57">
+        <v>-84.093416</v>
+      </c>
+      <c r="O57">
+        <v>-29.4326956</v>
+      </c>
+      <c r="P57">
+        <v>-54.6607204</v>
+      </c>
+      <c r="Q57">
+        <v>-53.6607204</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2528907901276941</v>
+      </c>
+      <c r="T57">
+        <v>0.9665412240736253</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.04402588218719668</v>
+      </c>
+      <c r="W57">
+        <v>0.2282866193336974</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1257882348205619</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2413584961909959</v>
+      </c>
+      <c r="C58">
+        <v>-38.29494672663753</v>
+      </c>
+      <c r="D58">
+        <v>351.5490532733625</v>
+      </c>
+      <c r="E58">
+        <v>390.144</v>
+      </c>
+      <c r="F58">
+        <v>410.144</v>
+      </c>
+      <c r="G58">
+        <v>20.3</v>
+      </c>
+      <c r="H58">
+        <v>712.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>13.1</v>
+      </c>
+      <c r="K58">
+        <v>1</v>
+      </c>
+      <c r="L58">
+        <v>12.1</v>
+      </c>
+      <c r="M58">
+        <v>97.94238720000001</v>
+      </c>
+      <c r="N58">
+        <v>-85.84238720000002</v>
+      </c>
+      <c r="O58">
+        <v>-30.04483552</v>
+      </c>
+      <c r="P58">
+        <v>-55.79755168000001</v>
+      </c>
+      <c r="Q58">
+        <v>-54.79755168000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2577564899033234</v>
+      </c>
+      <c r="T58">
+        <v>0.9885080700752984</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04323970571956816</v>
+      </c>
+      <c r="W58">
+        <v>0.2284743582741671</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1235420163416232</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2433584961909959</v>
+      </c>
+      <c r="C59">
+        <v>-49.0560960977898</v>
+      </c>
+      <c r="D59">
+        <v>348.1119039022102</v>
+      </c>
+      <c r="E59">
+        <v>397.468</v>
+      </c>
+      <c r="F59">
+        <v>417.468</v>
+      </c>
+      <c r="G59">
+        <v>20.3</v>
+      </c>
+      <c r="H59">
+        <v>712.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>13.1</v>
+      </c>
+      <c r="K59">
+        <v>1</v>
+      </c>
+      <c r="L59">
+        <v>12.1</v>
+      </c>
+      <c r="M59">
+        <v>99.69135840000001</v>
+      </c>
+      <c r="N59">
+        <v>-87.59135840000002</v>
+      </c>
+      <c r="O59">
+        <v>-30.65697544</v>
+      </c>
+      <c r="P59">
+        <v>-56.93438296000001</v>
+      </c>
+      <c r="Q59">
+        <v>-55.93438296000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.262848501296424</v>
+      </c>
+      <c r="T59">
+        <v>1.011496629844491</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04248111439115468</v>
+      </c>
+      <c r="W59">
+        <v>0.2286555098833923</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1213746125461562</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2453584961909959</v>
+      </c>
+      <c r="C60">
+        <v>-59.75068515920816</v>
+      </c>
+      <c r="D60">
+        <v>344.7413148407918</v>
+      </c>
+      <c r="E60">
+        <v>404.792</v>
+      </c>
+      <c r="F60">
+        <v>424.792</v>
+      </c>
+      <c r="G60">
+        <v>20.3</v>
+      </c>
+      <c r="H60">
+        <v>712.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>13.1</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60">
+        <v>12.1</v>
+      </c>
+      <c r="M60">
+        <v>101.4403296</v>
+      </c>
+      <c r="N60">
+        <v>-89.3403296</v>
+      </c>
+      <c r="O60">
+        <v>-31.26911536</v>
+      </c>
+      <c r="P60">
+        <v>-58.07121424</v>
+      </c>
+      <c r="Q60">
+        <v>-57.07121424</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2681829894225293</v>
+      </c>
+      <c r="T60">
+        <v>1.035579882936027</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.04174868138441064</v>
+      </c>
+      <c r="W60">
+        <v>0.2288304148854027</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1192819468126017</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2473584961909959</v>
+      </c>
+      <c r="C61">
+        <v>-70.38062877825962</v>
+      </c>
+      <c r="D61">
+        <v>341.4353712217404</v>
+      </c>
+      <c r="E61">
+        <v>412.116</v>
+      </c>
+      <c r="F61">
+        <v>432.116</v>
+      </c>
+      <c r="G61">
+        <v>20.3</v>
+      </c>
+      <c r="H61">
+        <v>712.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>13.1</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61">
+        <v>12.1</v>
+      </c>
+      <c r="M61">
+        <v>103.1893008</v>
+      </c>
+      <c r="N61">
+        <v>-91.0893008</v>
+      </c>
+      <c r="O61">
+        <v>-31.88125528</v>
+      </c>
+      <c r="P61">
+        <v>-59.20804552000001</v>
+      </c>
+      <c r="Q61">
+        <v>-58.20804552000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2737776964816154</v>
+      </c>
+      <c r="T61">
+        <v>1.060837928861296</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.04104107661518334</v>
+      </c>
+      <c r="W61">
+        <v>0.2289993909042942</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1172602189005237</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2493584961909959</v>
+      </c>
+      <c r="C62">
+        <v>-80.94776906847164</v>
+      </c>
+      <c r="D62">
+        <v>338.1922309315283</v>
+      </c>
+      <c r="E62">
+        <v>419.44</v>
+      </c>
+      <c r="F62">
+        <v>439.44</v>
+      </c>
+      <c r="G62">
+        <v>20.3</v>
+      </c>
+      <c r="H62">
+        <v>712.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>13.1</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62">
+        <v>12.1</v>
+      </c>
+      <c r="M62">
+        <v>104.938272</v>
+      </c>
+      <c r="N62">
+        <v>-92.838272</v>
+      </c>
+      <c r="O62">
+        <v>-32.4933952</v>
+      </c>
+      <c r="P62">
+        <v>-60.3448768</v>
+      </c>
+      <c r="Q62">
+        <v>-59.3448768</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2796521388936558</v>
+      </c>
+      <c r="T62">
+        <v>1.087358877082828</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04035705867159695</v>
+      </c>
+      <c r="W62">
+        <v>0.2291627343892227</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1153058819188484</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2513584961909959</v>
+      </c>
+      <c r="C63">
+        <v>-91.45387881230079</v>
+      </c>
+      <c r="D63">
+        <v>335.0101211876992</v>
+      </c>
+      <c r="E63">
+        <v>426.764</v>
+      </c>
+      <c r="F63">
+        <v>446.764</v>
+      </c>
+      <c r="G63">
+        <v>20.3</v>
+      </c>
+      <c r="H63">
+        <v>712.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>13.1</v>
+      </c>
+      <c r="K63">
+        <v>1</v>
+      </c>
+      <c r="L63">
+        <v>12.1</v>
+      </c>
+      <c r="M63">
+        <v>106.6872432</v>
+      </c>
+      <c r="N63">
+        <v>-94.5872432</v>
+      </c>
+      <c r="O63">
+        <v>-33.10553512</v>
+      </c>
+      <c r="P63">
+        <v>-61.48170808</v>
+      </c>
+      <c r="Q63">
+        <v>-60.48170808</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2858278347627238</v>
+      </c>
+      <c r="T63">
+        <v>1.115239873931106</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.03969546754583307</v>
+      </c>
+      <c r="W63">
+        <v>0.2293207223500551</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.113415621559523</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2533584961909959</v>
+      </c>
+      <c r="C64">
+        <v>-101.9006646924693</v>
+      </c>
+      <c r="D64">
+        <v>331.8873353075306</v>
+      </c>
+      <c r="E64">
+        <v>434.088</v>
+      </c>
+      <c r="F64">
+        <v>454.088</v>
+      </c>
+      <c r="G64">
+        <v>20.3</v>
+      </c>
+      <c r="H64">
+        <v>712.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>13.1</v>
+      </c>
+      <c r="K64">
+        <v>1</v>
+      </c>
+      <c r="L64">
+        <v>12.1</v>
+      </c>
+      <c r="M64">
+        <v>108.4362144</v>
+      </c>
+      <c r="N64">
+        <v>-96.3362144</v>
+      </c>
+      <c r="O64">
+        <v>-33.71767504</v>
+      </c>
+      <c r="P64">
+        <v>-62.61853936000001</v>
+      </c>
+      <c r="Q64">
+        <v>-61.61853936000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2923285672564798</v>
+      </c>
+      <c r="T64">
+        <v>1.144588291666135</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.03905521806928737</v>
+      </c>
+      <c r="W64">
+        <v>0.2294736139250542</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.111586337340821</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2553584961909959</v>
+      </c>
+      <c r="C65">
+        <v>-112.289770344245</v>
+      </c>
+      <c r="D65">
+        <v>328.822229655755</v>
+      </c>
+      <c r="E65">
+        <v>441.412</v>
+      </c>
+      <c r="F65">
+        <v>461.412</v>
+      </c>
+      <c r="G65">
+        <v>20.3</v>
+      </c>
+      <c r="H65">
+        <v>712.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>13.1</v>
+      </c>
+      <c r="K65">
+        <v>1</v>
+      </c>
+      <c r="L65">
+        <v>12.1</v>
+      </c>
+      <c r="M65">
+        <v>110.1851856</v>
+      </c>
+      <c r="N65">
+        <v>-98.0851856</v>
+      </c>
+      <c r="O65">
+        <v>-34.32981496</v>
+      </c>
+      <c r="P65">
+        <v>-63.75537064</v>
+      </c>
+      <c r="Q65">
+        <v>-62.75537064</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2991806906958441</v>
+      </c>
+      <c r="T65">
+        <v>1.175523110359814</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.03843529397294948</v>
+      </c>
+      <c r="W65">
+        <v>0.2296216517992597</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1098151256369985</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2573584961909959</v>
+      </c>
+      <c r="C66">
+        <v>-122.6227792401371</v>
+      </c>
+      <c r="D66">
+        <v>325.8132207598629</v>
+      </c>
+      <c r="E66">
+        <v>448.736</v>
+      </c>
+      <c r="F66">
+        <v>468.736</v>
+      </c>
+      <c r="G66">
+        <v>20.3</v>
+      </c>
+      <c r="H66">
+        <v>712.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>13.1</v>
+      </c>
+      <c r="K66">
+        <v>1</v>
+      </c>
+      <c r="L66">
+        <v>12.1</v>
+      </c>
+      <c r="M66">
+        <v>111.9341568</v>
+      </c>
+      <c r="N66">
+        <v>-99.8341568</v>
+      </c>
+      <c r="O66">
+        <v>-34.94195488</v>
+      </c>
+      <c r="P66">
+        <v>-64.89220192000001</v>
+      </c>
+      <c r="Q66">
+        <v>-63.89220192000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3064134876596176</v>
+      </c>
+      <c r="T66">
+        <v>1.208176530092032</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.03783474250462214</v>
+      </c>
+      <c r="W66">
+        <v>0.2297650634898963</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1080992642989204</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2593584961909959</v>
+      </c>
+      <c r="C67">
+        <v>-132.9012174176419</v>
+      </c>
+      <c r="D67">
+        <v>322.8587825823581</v>
+      </c>
+      <c r="E67">
+        <v>456.06</v>
+      </c>
+      <c r="F67">
+        <v>476.06</v>
+      </c>
+      <c r="G67">
+        <v>20.3</v>
+      </c>
+      <c r="H67">
+        <v>712.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>13.1</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67">
+        <v>12.1</v>
+      </c>
+      <c r="M67">
+        <v>113.683128</v>
+      </c>
+      <c r="N67">
+        <v>-101.583128</v>
+      </c>
+      <c r="O67">
+        <v>-35.5540948</v>
+      </c>
+      <c r="P67">
+        <v>-66.02903320000001</v>
+      </c>
+      <c r="Q67">
+        <v>-65.02903320000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3140595873070352</v>
+      </c>
+      <c r="T67">
+        <v>1.242695859523232</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03725266954301257</v>
+      </c>
+      <c r="W67">
+        <v>0.2299040625131286</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1064361986943215</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2613584961909959</v>
+      </c>
+      <c r="C68">
+        <v>-143.1265560599132</v>
+      </c>
+      <c r="D68">
+        <v>319.9574439400868</v>
+      </c>
+      <c r="E68">
+        <v>463.384</v>
+      </c>
+      <c r="F68">
+        <v>483.384</v>
+      </c>
+      <c r="G68">
+        <v>20.3</v>
+      </c>
+      <c r="H68">
+        <v>712.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>13.1</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>12.1</v>
+      </c>
+      <c r="M68">
+        <v>115.4320992</v>
+      </c>
+      <c r="N68">
+        <v>-103.3320992</v>
+      </c>
+      <c r="O68">
+        <v>-36.16623472000001</v>
+      </c>
+      <c r="P68">
+        <v>-67.16586448000001</v>
+      </c>
+      <c r="Q68">
+        <v>-66.16586448000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.322155457521948</v>
+      </c>
+      <c r="T68">
+        <v>1.279245737744504</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.03668823515599722</v>
+      </c>
+      <c r="W68">
+        <v>0.2300388494447479</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1048235290171349</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2633584961909959</v>
+      </c>
+      <c r="C69">
+        <v>-153.3002139385262</v>
+      </c>
+      <c r="D69">
+        <v>317.1077860614738</v>
+      </c>
+      <c r="E69">
+        <v>470.708</v>
+      </c>
+      <c r="F69">
+        <v>490.708</v>
+      </c>
+      <c r="G69">
+        <v>20.3</v>
+      </c>
+      <c r="H69">
+        <v>712.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>13.1</v>
+      </c>
+      <c r="K69">
+        <v>1</v>
+      </c>
+      <c r="L69">
+        <v>12.1</v>
+      </c>
+      <c r="M69">
+        <v>117.1810704</v>
+      </c>
+      <c r="N69">
+        <v>-105.0810704</v>
+      </c>
+      <c r="O69">
+        <v>-36.77837464</v>
+      </c>
+      <c r="P69">
+        <v>-68.30269576000001</v>
+      </c>
+      <c r="Q69">
+        <v>-67.30269576000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3307419865377646</v>
+      </c>
+      <c r="T69">
+        <v>1.318010760100398</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03614064955665398</v>
+      </c>
+      <c r="W69">
+        <v>0.230169612885871</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.103258998733297</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2653584961909959</v>
+      </c>
+      <c r="C70">
+        <v>-163.4235597268576</v>
+      </c>
+      <c r="D70">
+        <v>314.3084402731424</v>
+      </c>
+      <c r="E70">
+        <v>478.032</v>
+      </c>
+      <c r="F70">
+        <v>498.032</v>
+      </c>
+      <c r="G70">
+        <v>20.3</v>
+      </c>
+      <c r="H70">
+        <v>712.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>13.1</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>12.1</v>
+      </c>
+      <c r="M70">
+        <v>118.9300416</v>
+      </c>
+      <c r="N70">
+        <v>-106.8300416</v>
+      </c>
+      <c r="O70">
+        <v>-37.39051456</v>
+      </c>
+      <c r="P70">
+        <v>-69.43952704000002</v>
+      </c>
+      <c r="Q70">
+        <v>-68.43952704000002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3398651736170697</v>
+      </c>
+      <c r="T70">
+        <v>1.359198596353536</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.03560916941611495</v>
+      </c>
+      <c r="W70">
+        <v>0.2302965303434318</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1017404840460426</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2673584961909959</v>
+      </c>
+      <c r="C71">
+        <v>-173.4979141920049</v>
+      </c>
+      <c r="D71">
+        <v>311.5580858079951</v>
+      </c>
+      <c r="E71">
+        <v>485.3560000000001</v>
+      </c>
+      <c r="F71">
+        <v>505.3560000000001</v>
+      </c>
+      <c r="G71">
+        <v>20.3</v>
+      </c>
+      <c r="H71">
+        <v>712.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>13.1</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
+      </c>
+      <c r="L71">
+        <v>12.1</v>
+      </c>
+      <c r="M71">
+        <v>120.6790128</v>
+      </c>
+      <c r="N71">
+        <v>-108.5790128</v>
+      </c>
+      <c r="O71">
+        <v>-38.00265448000001</v>
+      </c>
+      <c r="P71">
+        <v>-70.57635832000003</v>
+      </c>
+      <c r="Q71">
+        <v>-69.57635832000003</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3495769534111688</v>
+      </c>
+      <c r="T71">
+        <v>1.40304371236494</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03509309449704082</v>
+      </c>
+      <c r="W71">
+        <v>0.2304197690341067</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1002659842772594</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2693584961909959</v>
+      </c>
+      <c r="C72">
+        <v>-183.5245522726238</v>
+      </c>
+      <c r="D72">
+        <v>308.8554477273763</v>
+      </c>
+      <c r="E72">
+        <v>492.6800000000001</v>
+      </c>
+      <c r="F72">
+        <v>512.6800000000001</v>
+      </c>
+      <c r="G72">
+        <v>20.3</v>
+      </c>
+      <c r="H72">
+        <v>712.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>13.1</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+      <c r="L72">
+        <v>12.1</v>
+      </c>
+      <c r="M72">
+        <v>122.427984</v>
+      </c>
+      <c r="N72">
+        <v>-110.327984</v>
+      </c>
+      <c r="O72">
+        <v>-38.61479440000001</v>
+      </c>
+      <c r="P72">
+        <v>-71.71318960000002</v>
+      </c>
+      <c r="Q72">
+        <v>-70.71318960000002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3599361851915411</v>
+      </c>
+      <c r="T72">
+        <v>1.449811836110438</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03459176457565452</v>
+      </c>
+      <c r="W72">
+        <v>0.2305394866193337</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.09883361307329863</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2713584961909959</v>
+      </c>
+      <c r="C73">
+        <v>-193.5047050495467</v>
+      </c>
+      <c r="D73">
+        <v>306.1992949504532</v>
+      </c>
+      <c r="E73">
+        <v>500.0039999999999</v>
+      </c>
+      <c r="F73">
+        <v>520.0039999999999</v>
+      </c>
+      <c r="G73">
+        <v>20.3</v>
+      </c>
+      <c r="H73">
+        <v>712.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>13.1</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="L73">
+        <v>12.1</v>
+      </c>
+      <c r="M73">
+        <v>124.1769552</v>
+      </c>
+      <c r="N73">
+        <v>-112.0769552</v>
+      </c>
+      <c r="O73">
+        <v>-39.22693431999999</v>
+      </c>
+      <c r="P73">
+        <v>-72.85002087999999</v>
+      </c>
+      <c r="Q73">
+        <v>-71.85002087999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.37100984674987</v>
+      </c>
+      <c r="T73">
+        <v>1.499805347700452</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03410455662388475</v>
+      </c>
+      <c r="W73">
+        <v>0.2306558318782163</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.09744159035395639</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2733584961909959</v>
+      </c>
+      <c r="C74">
+        <v>-203.4395616155875</v>
+      </c>
+      <c r="D74">
+        <v>303.5884383844124</v>
+      </c>
+      <c r="E74">
+        <v>507.328</v>
+      </c>
+      <c r="F74">
+        <v>527.328</v>
+      </c>
+      <c r="G74">
+        <v>20.3</v>
+      </c>
+      <c r="H74">
+        <v>712.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>13.1</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+      <c r="L74">
+        <v>12.1</v>
+      </c>
+      <c r="M74">
+        <v>125.9259264</v>
+      </c>
+      <c r="N74">
+        <v>-113.8259264</v>
+      </c>
+      <c r="O74">
+        <v>-39.83907424</v>
+      </c>
+      <c r="P74">
+        <v>-73.98685216000001</v>
+      </c>
+      <c r="Q74">
+        <v>-72.98685216000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3828744841337939</v>
+      </c>
+      <c r="T74">
+        <v>1.55336982440404</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0336308822263308</v>
+      </c>
+      <c r="W74">
+        <v>0.2307689453243522</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.09608823493237362</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2753584961909959</v>
+      </c>
+      <c r="C75">
+        <v>-213.3302708504932</v>
+      </c>
+      <c r="D75">
+        <v>301.0217291495068</v>
+      </c>
+      <c r="E75">
+        <v>514.6519999999999</v>
+      </c>
+      <c r="F75">
+        <v>534.6519999999999</v>
+      </c>
+      <c r="G75">
+        <v>20.3</v>
+      </c>
+      <c r="H75">
+        <v>712.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>13.1</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="L75">
+        <v>12.1</v>
+      </c>
+      <c r="M75">
+        <v>127.6748976</v>
+      </c>
+      <c r="N75">
+        <v>-115.5748976</v>
+      </c>
+      <c r="O75">
+        <v>-40.45121416</v>
+      </c>
+      <c r="P75">
+        <v>-75.12368344000001</v>
+      </c>
+      <c r="Q75">
+        <v>-74.12368344000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3956179835461566</v>
+      </c>
+      <c r="T75">
+        <v>1.610902040122708</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03317018520953174</v>
+      </c>
+      <c r="W75">
+        <v>0.2308789597719638</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.09477195774151925</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2773584961909959</v>
+      </c>
+      <c r="C76">
+        <v>-223.1779431066136</v>
+      </c>
+      <c r="D76">
+        <v>298.4980568933864</v>
+      </c>
+      <c r="E76">
+        <v>521.976</v>
+      </c>
+      <c r="F76">
+        <v>541.976</v>
+      </c>
+      <c r="G76">
+        <v>20.3</v>
+      </c>
+      <c r="H76">
+        <v>712.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>13.1</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
+      </c>
+      <c r="L76">
+        <v>12.1</v>
+      </c>
+      <c r="M76">
+        <v>129.4238688</v>
+      </c>
+      <c r="N76">
+        <v>-117.3238688</v>
+      </c>
+      <c r="O76">
+        <v>-41.06335408</v>
+      </c>
+      <c r="P76">
+        <v>-76.26051472</v>
+      </c>
+      <c r="Q76">
+        <v>-75.26051472</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4093417521440857</v>
+      </c>
+      <c r="T76">
+        <v>1.672859810896659</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03272193946345699</v>
+      </c>
+      <c r="W76">
+        <v>0.2309860008561265</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.09349125560987703</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2793584961909959</v>
+      </c>
+      <c r="C77">
+        <v>-232.9836518104823</v>
+      </c>
+      <c r="D77">
+        <v>296.0163481895177</v>
+      </c>
+      <c r="E77">
+        <v>529.3</v>
+      </c>
+      <c r="F77">
+        <v>549.3</v>
+      </c>
+      <c r="G77">
+        <v>20.3</v>
+      </c>
+      <c r="H77">
+        <v>712.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>13.1</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="L77">
+        <v>12.1</v>
+      </c>
+      <c r="M77">
+        <v>131.17284</v>
+      </c>
+      <c r="N77">
+        <v>-119.07284</v>
+      </c>
+      <c r="O77">
+        <v>-41.675494</v>
+      </c>
+      <c r="P77">
+        <v>-77.39734600000001</v>
+      </c>
+      <c r="Q77">
+        <v>-76.39734600000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4241634222298492</v>
+      </c>
+      <c r="T77">
+        <v>1.739774203332525</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03228564693727756</v>
+      </c>
+      <c r="W77">
+        <v>0.2310901875113781</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.09224470553507869</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.281358496190996</v>
+      </c>
+      <c r="C78">
+        <v>-242.7484349851639</v>
+      </c>
+      <c r="D78">
+        <v>293.5755650148361</v>
+      </c>
+      <c r="E78">
+        <v>536.624</v>
+      </c>
+      <c r="F78">
+        <v>556.624</v>
+      </c>
+      <c r="G78">
+        <v>20.3</v>
+      </c>
+      <c r="H78">
+        <v>712.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>13.1</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="L78">
+        <v>12.1</v>
+      </c>
+      <c r="M78">
+        <v>132.9218112</v>
+      </c>
+      <c r="N78">
+        <v>-120.8218112</v>
+      </c>
+      <c r="O78">
+        <v>-42.28763392</v>
+      </c>
+      <c r="P78">
+        <v>-78.53417728000001</v>
+      </c>
+      <c r="Q78">
+        <v>-77.53417728000001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4402202314894264</v>
+      </c>
+      <c r="T78">
+        <v>1.812264795138047</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03186083579336601</v>
+      </c>
+      <c r="W78">
+        <v>0.2311916324125442</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.09103095940961714</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.283358496190996</v>
+      </c>
+      <c r="C79">
+        <v>-252.4732966979016</v>
+      </c>
+      <c r="D79">
+        <v>291.1747033020984</v>
+      </c>
+      <c r="E79">
+        <v>543.948</v>
+      </c>
+      <c r="F79">
+        <v>563.948</v>
+      </c>
+      <c r="G79">
+        <v>20.3</v>
+      </c>
+      <c r="H79">
+        <v>712.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>13.1</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>12.1</v>
+      </c>
+      <c r="M79">
+        <v>134.6707824</v>
+      </c>
+      <c r="N79">
+        <v>-122.5707824</v>
+      </c>
+      <c r="O79">
+        <v>-42.89977384</v>
+      </c>
+      <c r="P79">
+        <v>-79.67100856000002</v>
+      </c>
+      <c r="Q79">
+        <v>-78.67100856000002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4576732850324449</v>
+      </c>
+      <c r="T79">
+        <v>1.891058916665789</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03144705870514048</v>
+      </c>
+      <c r="W79">
+        <v>0.2312904423812125</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.08984873915754421</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2853584961909958</v>
+      </c>
+      <c r="C80">
+        <v>-262.1592084373091</v>
+      </c>
+      <c r="D80">
+        <v>288.812791562691</v>
+      </c>
+      <c r="E80">
+        <v>551.272</v>
+      </c>
+      <c r="F80">
+        <v>571.272</v>
+      </c>
+      <c r="G80">
+        <v>20.3</v>
+      </c>
+      <c r="H80">
+        <v>712.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>13.1</v>
+      </c>
+      <c r="K80">
+        <v>1</v>
+      </c>
+      <c r="L80">
+        <v>12.1</v>
+      </c>
+      <c r="M80">
+        <v>136.4197536</v>
+      </c>
+      <c r="N80">
+        <v>-124.3197536</v>
+      </c>
+      <c r="O80">
+        <v>-43.51191376</v>
+      </c>
+      <c r="P80">
+        <v>-80.80783984000001</v>
+      </c>
+      <c r="Q80">
+        <v>-79.80783984000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4767129798066468</v>
+      </c>
+      <c r="T80">
+        <v>1.977016140150597</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03104389128584381</v>
+      </c>
+      <c r="W80">
+        <v>0.2313867187609405</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.08869683224526803</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.287358496190996</v>
+      </c>
+      <c r="C81">
+        <v>-271.8071104240734</v>
+      </c>
+      <c r="D81">
+        <v>286.4888895759266</v>
+      </c>
+      <c r="E81">
+        <v>558.596</v>
+      </c>
+      <c r="F81">
+        <v>578.596</v>
+      </c>
+      <c r="G81">
+        <v>20.3</v>
+      </c>
+      <c r="H81">
+        <v>712.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>13.1</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="L81">
+        <v>12.1</v>
+      </c>
+      <c r="M81">
+        <v>138.1687248</v>
+      </c>
+      <c r="N81">
+        <v>-126.0687248</v>
+      </c>
+      <c r="O81">
+        <v>-44.12405368</v>
+      </c>
+      <c r="P81">
+        <v>-81.94467112000001</v>
+      </c>
+      <c r="Q81">
+        <v>-80.94467112000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4975659788450588</v>
+      </c>
+      <c r="T81">
+        <v>2.071159765872054</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03065093063665591</v>
+      </c>
+      <c r="W81">
+        <v>0.2314805577639666</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.08757408753330254</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.289358496190996</v>
+      </c>
+      <c r="C82">
+        <v>-281.4179128588832</v>
+      </c>
+      <c r="D82">
+        <v>284.2020871411167</v>
+      </c>
+      <c r="E82">
+        <v>565.92</v>
+      </c>
+      <c r="F82">
+        <v>585.92</v>
+      </c>
+      <c r="G82">
+        <v>20.3</v>
+      </c>
+      <c r="H82">
+        <v>712.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>13.1</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>12.1</v>
+      </c>
+      <c r="M82">
+        <v>139.917696</v>
+      </c>
+      <c r="N82">
+        <v>-127.817696</v>
+      </c>
+      <c r="O82">
+        <v>-44.7361936</v>
+      </c>
+      <c r="P82">
+        <v>-83.08150240000001</v>
+      </c>
+      <c r="Q82">
+        <v>-82.08150240000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5205042777873117</v>
+      </c>
+      <c r="T82">
+        <v>2.174717754165657</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03026779400369771</v>
+      </c>
+      <c r="W82">
+        <v>0.231572050791917</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.08647941143913629</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.291358496190996</v>
+      </c>
+      <c r="C83">
+        <v>-290.9924971110653</v>
+      </c>
+      <c r="D83">
+        <v>281.9515028889347</v>
+      </c>
+      <c r="E83">
+        <v>573.244</v>
+      </c>
+      <c r="F83">
+        <v>593.244</v>
+      </c>
+      <c r="G83">
+        <v>20.3</v>
+      </c>
+      <c r="H83">
+        <v>712.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>13.1</v>
+      </c>
+      <c r="K83">
+        <v>1</v>
+      </c>
+      <c r="L83">
+        <v>12.1</v>
+      </c>
+      <c r="M83">
+        <v>141.6666672</v>
+      </c>
+      <c r="N83">
+        <v>-129.5666672</v>
+      </c>
+      <c r="O83">
+        <v>-45.34833352</v>
+      </c>
+      <c r="P83">
+        <v>-84.21833368</v>
+      </c>
+      <c r="Q83">
+        <v>-83.21833368</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5458571345129597</v>
+      </c>
+      <c r="T83">
+        <v>2.28917658333227</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.02989411753451626</v>
+      </c>
+      <c r="W83">
+        <v>0.2316612847327575</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.08541176438433218</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2933584961909959</v>
+      </c>
+      <c r="C84">
+        <v>-300.5317168511864</v>
+      </c>
+      <c r="D84">
+        <v>279.7362831488135</v>
+      </c>
+      <c r="E84">
+        <v>580.568</v>
+      </c>
+      <c r="F84">
+        <v>600.568</v>
+      </c>
+      <c r="G84">
+        <v>20.3</v>
+      </c>
+      <c r="H84">
+        <v>712.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>13.1</v>
+      </c>
+      <c r="K84">
+        <v>1</v>
+      </c>
+      <c r="L84">
+        <v>12.1</v>
+      </c>
+      <c r="M84">
+        <v>143.4156384</v>
+      </c>
+      <c r="N84">
+        <v>-131.3156384</v>
+      </c>
+      <c r="O84">
+        <v>-45.96047344</v>
+      </c>
+      <c r="P84">
+        <v>-85.35516496000001</v>
+      </c>
+      <c r="Q84">
+        <v>-84.35516496000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5740269753192351</v>
+      </c>
+      <c r="T84">
+        <v>2.416353060184063</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02952955512555874</v>
+      </c>
+      <c r="W84">
+        <v>0.2317483422360166</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.08437015750159638</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2953584961909959</v>
+      </c>
+      <c r="C85">
+        <v>-310.0363991306816</v>
+      </c>
+      <c r="D85">
+        <v>277.5556008693184</v>
+      </c>
+      <c r="E85">
+        <v>587.8920000000001</v>
+      </c>
+      <c r="F85">
+        <v>607.8920000000001</v>
+      </c>
+      <c r="G85">
+        <v>20.3</v>
+      </c>
+      <c r="H85">
+        <v>712.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>13.1</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+      <c r="L85">
+        <v>12.1</v>
+      </c>
+      <c r="M85">
+        <v>145.1646096</v>
+      </c>
+      <c r="N85">
+        <v>-133.0646096</v>
+      </c>
+      <c r="O85">
+        <v>-46.57261336000001</v>
+      </c>
+      <c r="P85">
+        <v>-86.49199624000002</v>
+      </c>
+      <c r="Q85">
+        <v>-85.49199624000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6055109150438962</v>
+      </c>
+      <c r="T85">
+        <v>2.558491475489009</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.02917377735296164</v>
+      </c>
+      <c r="W85">
+        <v>0.2318333019681128</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.08335364957989033</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2973584961909959</v>
+      </c>
+      <c r="C86">
+        <v>-319.5073454113739</v>
+      </c>
+      <c r="D86">
+        <v>275.4086545886261</v>
+      </c>
+      <c r="E86">
+        <v>595.216</v>
+      </c>
+      <c r="F86">
+        <v>615.216</v>
+      </c>
+      <c r="G86">
+        <v>20.3</v>
+      </c>
+      <c r="H86">
+        <v>712.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>13.1</v>
+      </c>
+      <c r="K86">
+        <v>1</v>
+      </c>
+      <c r="L86">
+        <v>12.1</v>
+      </c>
+      <c r="M86">
+        <v>146.9135808</v>
+      </c>
+      <c r="N86">
+        <v>-134.8135808</v>
+      </c>
+      <c r="O86">
+        <v>-47.18475328</v>
+      </c>
+      <c r="P86">
+        <v>-87.62882752000002</v>
+      </c>
+      <c r="Q86">
+        <v>-86.62882752000002</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6409303472341394</v>
+      </c>
+      <c r="T86">
+        <v>2.71839719270707</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02882647047971211</v>
+      </c>
+      <c r="W86">
+        <v>0.2319162388494448</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.08236134422774888</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2993584961909959</v>
+      </c>
+      <c r="C87">
+        <v>-328.9453325475809</v>
+      </c>
+      <c r="D87">
+        <v>273.294667452419</v>
+      </c>
+      <c r="E87">
+        <v>602.54</v>
+      </c>
+      <c r="F87">
+        <v>622.54</v>
+      </c>
+      <c r="G87">
+        <v>20.3</v>
+      </c>
+      <c r="H87">
+        <v>712.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>13.1</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>12.1</v>
+      </c>
+      <c r="M87">
+        <v>148.662552</v>
+      </c>
+      <c r="N87">
+        <v>-136.562552</v>
+      </c>
+      <c r="O87">
+        <v>-47.7968932</v>
+      </c>
+      <c r="P87">
+        <v>-88.76565880000001</v>
+      </c>
+      <c r="Q87">
+        <v>-87.76565880000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.6810723703830819</v>
+      </c>
+      <c r="T87">
+        <v>2.899623672220875</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02848733553289196</v>
+      </c>
+      <c r="W87">
+        <v>0.2319972242747454</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.08139238723683417</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3013584961909959</v>
+      </c>
+      <c r="C88">
+        <v>-338.3511137233355</v>
+      </c>
+      <c r="D88">
+        <v>271.2128862766644</v>
+      </c>
+      <c r="E88">
+        <v>609.8639999999999</v>
+      </c>
+      <c r="F88">
+        <v>629.8639999999999</v>
+      </c>
+      <c r="G88">
+        <v>20.3</v>
+      </c>
+      <c r="H88">
+        <v>712.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>13.1</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88">
+        <v>12.1</v>
+      </c>
+      <c r="M88">
+        <v>150.4115232</v>
+      </c>
+      <c r="N88">
+        <v>-138.3115232</v>
+      </c>
+      <c r="O88">
+        <v>-48.40903311999999</v>
+      </c>
+      <c r="P88">
+        <v>-89.90249007999999</v>
+      </c>
+      <c r="Q88">
+        <v>-88.90249007999999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7269489682675878</v>
+      </c>
+      <c r="T88">
+        <v>3.106739648808081</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.0281560874453002</v>
+      </c>
+      <c r="W88">
+        <v>0.2320763263180623</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.08044596412942917</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3033584961909959</v>
+      </c>
+      <c r="C89">
+        <v>-347.7254193470935</v>
+      </c>
+      <c r="D89">
+        <v>269.1625806529065</v>
+      </c>
+      <c r="E89">
+        <v>617.188</v>
+      </c>
+      <c r="F89">
+        <v>637.188</v>
+      </c>
+      <c r="G89">
+        <v>20.3</v>
+      </c>
+      <c r="H89">
+        <v>712.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>13.1</v>
+      </c>
+      <c r="K89">
+        <v>1</v>
+      </c>
+      <c r="L89">
+        <v>12.1</v>
+      </c>
+      <c r="M89">
+        <v>152.1604944</v>
+      </c>
+      <c r="N89">
+        <v>-140.0604944</v>
+      </c>
+      <c r="O89">
+        <v>-49.02117304</v>
+      </c>
+      <c r="P89">
+        <v>-91.03932136</v>
+      </c>
+      <c r="Q89">
+        <v>-90.03932136</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.7798835042881715</v>
+      </c>
+      <c r="T89">
+        <v>3.345719621793317</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02783245425627376</v>
+      </c>
+      <c r="W89">
+        <v>0.2321536099236018</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.0795212978750679</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3053584961909959</v>
+      </c>
+      <c r="C90">
+        <v>-357.0689579061648</v>
+      </c>
+      <c r="D90">
+        <v>267.1430420938351</v>
+      </c>
+      <c r="E90">
+        <v>624.5119999999999</v>
+      </c>
+      <c r="F90">
+        <v>644.5119999999999</v>
+      </c>
+      <c r="G90">
+        <v>20.3</v>
+      </c>
+      <c r="H90">
+        <v>712.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>13.1</v>
+      </c>
+      <c r="K90">
+        <v>1</v>
+      </c>
+      <c r="L90">
+        <v>12.1</v>
+      </c>
+      <c r="M90">
+        <v>153.9094656</v>
+      </c>
+      <c r="N90">
+        <v>-141.8094656</v>
+      </c>
+      <c r="O90">
+        <v>-49.63331296</v>
+      </c>
+      <c r="P90">
+        <v>-92.17615264000001</v>
+      </c>
+      <c r="Q90">
+        <v>-91.17615264000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.8416404629788528</v>
+      </c>
+      <c r="T90">
+        <v>3.624529590276095</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02751617636699792</v>
+      </c>
+      <c r="W90">
+        <v>0.2322291370835609</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.07861764676285121</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3073584961909959</v>
+      </c>
+      <c r="C91">
+        <v>-366.3824167829665</v>
+      </c>
+      <c r="D91">
+        <v>265.1535832170335</v>
+      </c>
+      <c r="E91">
+        <v>631.836</v>
+      </c>
+      <c r="F91">
+        <v>651.836</v>
+      </c>
+      <c r="G91">
+        <v>20.3</v>
+      </c>
+      <c r="H91">
+        <v>712.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>13.1</v>
+      </c>
+      <c r="K91">
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>12.1</v>
+      </c>
+      <c r="M91">
+        <v>155.6584368</v>
+      </c>
+      <c r="N91">
+        <v>-143.5584368</v>
+      </c>
+      <c r="O91">
+        <v>-50.24545288</v>
+      </c>
+      <c r="P91">
+        <v>-93.31298392000001</v>
+      </c>
+      <c r="Q91">
+        <v>-92.31298392000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.9146259596132937</v>
+      </c>
+      <c r="T91">
+        <v>3.954032280301194</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02720700584602042</v>
+      </c>
+      <c r="W91">
+        <v>0.2323029670039703</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.07773430241720114</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3093584961909959</v>
+      </c>
+      <c r="C92">
+        <v>-375.6664630350704</v>
+      </c>
+      <c r="D92">
+        <v>263.1935369649295</v>
+      </c>
+      <c r="E92">
+        <v>639.16</v>
+      </c>
+      <c r="F92">
+        <v>659.16</v>
+      </c>
+      <c r="G92">
+        <v>20.3</v>
+      </c>
+      <c r="H92">
+        <v>712.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>13.1</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+      <c r="L92">
+        <v>12.1</v>
+      </c>
+      <c r="M92">
+        <v>157.407408</v>
+      </c>
+      <c r="N92">
+        <v>-145.307408</v>
+      </c>
+      <c r="O92">
+        <v>-50.8575928</v>
+      </c>
+      <c r="P92">
+        <v>-94.44981520000002</v>
+      </c>
+      <c r="Q92">
+        <v>-93.44981520000002</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.002208555574623</v>
+      </c>
+      <c r="T92">
+        <v>4.349435508331314</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02690470578106463</v>
+      </c>
+      <c r="W92">
+        <v>0.2323751562594818</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.07687058794589896</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3113584961909959</v>
+      </c>
+      <c r="C93">
+        <v>-384.9217441409107</v>
+      </c>
+      <c r="D93">
+        <v>261.2622558590894</v>
+      </c>
+      <c r="E93">
+        <v>646.484</v>
+      </c>
+      <c r="F93">
+        <v>666.484</v>
+      </c>
+      <c r="G93">
+        <v>20.3</v>
+      </c>
+      <c r="H93">
+        <v>712.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>13.1</v>
+      </c>
+      <c r="K93">
+        <v>1</v>
+      </c>
+      <c r="L93">
+        <v>12.1</v>
+      </c>
+      <c r="M93">
+        <v>159.1563792</v>
+      </c>
+      <c r="N93">
+        <v>-147.0563792</v>
+      </c>
+      <c r="O93">
+        <v>-51.46973272</v>
+      </c>
+      <c r="P93">
+        <v>-95.58664648000001</v>
+      </c>
+      <c r="Q93">
+        <v>-94.58664648000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.10925395063847</v>
+      </c>
+      <c r="T93">
+        <v>4.832706120368127</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02660904967358041</v>
+      </c>
+      <c r="W93">
+        <v>0.232445758937949</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.07602585621022973</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3133584961909959</v>
+      </c>
+      <c r="C94">
+        <v>-394.1488887128953</v>
+      </c>
+      <c r="D94">
+        <v>259.3591112871047</v>
+      </c>
+      <c r="E94">
+        <v>653.808</v>
+      </c>
+      <c r="F94">
+        <v>673.808</v>
+      </c>
+      <c r="G94">
+        <v>20.3</v>
+      </c>
+      <c r="H94">
+        <v>712.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>13.1</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
+      <c r="L94">
+        <v>12.1</v>
+      </c>
+      <c r="M94">
+        <v>160.9053504</v>
+      </c>
+      <c r="N94">
+        <v>-148.8053504</v>
+      </c>
+      <c r="O94">
+        <v>-52.08187264</v>
+      </c>
+      <c r="P94">
+        <v>-96.72347776000001</v>
+      </c>
+      <c r="Q94">
+        <v>-95.72347776000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.243060694468279</v>
+      </c>
+      <c r="T94">
+        <v>5.436794385414144</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02631982087278062</v>
+      </c>
+      <c r="W94">
+        <v>0.23251482677558</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.07519948820794464</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3153584961909959</v>
+      </c>
+      <c r="C95">
+        <v>-403.3485071795795</v>
+      </c>
+      <c r="D95">
+        <v>257.4834928204206</v>
+      </c>
+      <c r="E95">
+        <v>661.1320000000001</v>
+      </c>
+      <c r="F95">
+        <v>681.1320000000001</v>
+      </c>
+      <c r="G95">
+        <v>20.3</v>
+      </c>
+      <c r="H95">
+        <v>712.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>13.1</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="L95">
+        <v>12.1</v>
+      </c>
+      <c r="M95">
+        <v>162.6543216</v>
+      </c>
+      <c r="N95">
+        <v>-150.5543216</v>
+      </c>
+      <c r="O95">
+        <v>-52.69401256000001</v>
+      </c>
+      <c r="P95">
+        <v>-97.86030904000003</v>
+      </c>
+      <c r="Q95">
+        <v>-96.86030904000003</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.415097936535177</v>
+      </c>
+      <c r="T95">
+        <v>6.213479297616166</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02603681204619158</v>
+      </c>
+      <c r="W95">
+        <v>0.2325824092833695</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.07439089156054735</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3173584961909959</v>
+      </c>
+      <c r="C96">
+        <v>-412.5211924384478</v>
+      </c>
+      <c r="D96">
+        <v>255.6348075615522</v>
+      </c>
+      <c r="E96">
+        <v>668.456</v>
+      </c>
+      <c r="F96">
+        <v>688.456</v>
+      </c>
+      <c r="G96">
+        <v>20.3</v>
+      </c>
+      <c r="H96">
+        <v>712.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>13.1</v>
+      </c>
+      <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="L96">
+        <v>12.1</v>
+      </c>
+      <c r="M96">
+        <v>164.4032928</v>
+      </c>
+      <c r="N96">
+        <v>-152.3032928</v>
+      </c>
+      <c r="O96">
+        <v>-53.30615248</v>
+      </c>
+      <c r="P96">
+        <v>-98.99714032</v>
+      </c>
+      <c r="Q96">
+        <v>-97.99714032</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.644480925957707</v>
+      </c>
+      <c r="T96">
+        <v>7.249059180552195</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02575982468399805</v>
+      </c>
+      <c r="W96">
+        <v>0.2326485538654613</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.07359949909713726</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3193584961909959</v>
+      </c>
+      <c r="C97">
+        <v>-421.6675204807789</v>
+      </c>
+      <c r="D97">
+        <v>253.8124795192211</v>
+      </c>
+      <c r="E97">
+        <v>675.78</v>
+      </c>
+      <c r="F97">
+        <v>695.78</v>
+      </c>
+      <c r="G97">
+        <v>20.3</v>
+      </c>
+      <c r="H97">
+        <v>712.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>13.1</v>
+      </c>
+      <c r="K97">
+        <v>1</v>
+      </c>
+      <c r="L97">
+        <v>12.1</v>
+      </c>
+      <c r="M97">
+        <v>166.152264</v>
+      </c>
+      <c r="N97">
+        <v>-154.052264</v>
+      </c>
+      <c r="O97">
+        <v>-53.9182924</v>
+      </c>
+      <c r="P97">
+        <v>-100.1339716</v>
+      </c>
+      <c r="Q97">
+        <v>-99.13397160000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.965617111149249</v>
+      </c>
+      <c r="T97">
+        <v>8.698871016662638</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02548866863469281</v>
+      </c>
+      <c r="W97">
+        <v>0.2327133059300354</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.07282476752769373</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3213584961909959</v>
+      </c>
+      <c r="C98">
+        <v>-430.7880509899705</v>
+      </c>
+      <c r="D98">
+        <v>252.0159490100294</v>
+      </c>
+      <c r="E98">
+        <v>683.1039999999999</v>
+      </c>
+      <c r="F98">
+        <v>703.1039999999999</v>
+      </c>
+      <c r="G98">
+        <v>20.3</v>
+      </c>
+      <c r="H98">
+        <v>712.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>13.1</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>12.1</v>
+      </c>
+      <c r="M98">
+        <v>167.9012352</v>
+      </c>
+      <c r="N98">
+        <v>-155.8012352</v>
+      </c>
+      <c r="O98">
+        <v>-54.53043232</v>
+      </c>
+      <c r="P98">
+        <v>-101.27080288</v>
+      </c>
+      <c r="Q98">
+        <v>-100.27080288</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.447321388936555</v>
+      </c>
+      <c r="T98">
+        <v>10.87358877082827</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02522316166974809</v>
+      </c>
+      <c r="W98">
+        <v>0.2327767089932642</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.07206617619928024</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3233584961909959</v>
+      </c>
+      <c r="C99">
+        <v>-439.8833279146341</v>
+      </c>
+      <c r="D99">
+        <v>250.2446720853659</v>
+      </c>
+      <c r="E99">
+        <v>690.428</v>
+      </c>
+      <c r="F99">
+        <v>710.428</v>
+      </c>
+      <c r="G99">
+        <v>20.3</v>
+      </c>
+      <c r="H99">
+        <v>712.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>13.1</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99">
+        <v>12.1</v>
+      </c>
+      <c r="M99">
+        <v>169.6502064</v>
+      </c>
+      <c r="N99">
+        <v>-157.5502064</v>
+      </c>
+      <c r="O99">
+        <v>-55.14257224</v>
+      </c>
+      <c r="P99">
+        <v>-102.40763416</v>
+      </c>
+      <c r="Q99">
+        <v>-101.40763416</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.250161851915408</v>
+      </c>
+      <c r="T99">
+        <v>14.49811836110437</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02496312907521461</v>
+      </c>
+      <c r="W99">
+        <v>0.2328388047768388</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.07132322592918461</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3253584961909959</v>
+      </c>
+      <c r="C100">
+        <v>-448.9538800176894</v>
+      </c>
+      <c r="D100">
+        <v>248.4981199823106</v>
+      </c>
+      <c r="E100">
+        <v>697.752</v>
+      </c>
+      <c r="F100">
+        <v>717.752</v>
+      </c>
+      <c r="G100">
+        <v>20.3</v>
+      </c>
+      <c r="H100">
+        <v>712.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>13.1</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>12.1</v>
+      </c>
+      <c r="M100">
+        <v>171.3991776</v>
+      </c>
+      <c r="N100">
+        <v>-159.2991776</v>
+      </c>
+      <c r="O100">
+        <v>-55.75471216</v>
+      </c>
+      <c r="P100">
+        <v>-103.54446544</v>
+      </c>
+      <c r="Q100">
+        <v>-102.54446544</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.855842777873111</v>
+      </c>
+      <c r="T100">
+        <v>21.74717754165654</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02470840326832466</v>
+      </c>
+      <c r="W100">
+        <v>0.2328996332995241</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.07059543790949896</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3273584961909959</v>
+      </c>
+      <c r="C101">
+        <v>-458.0002214026253</v>
+      </c>
+      <c r="D101">
+        <v>246.7757785973747</v>
+      </c>
+      <c r="E101">
+        <v>705.076</v>
+      </c>
+      <c r="F101">
+        <v>725.076</v>
+      </c>
+      <c r="G101">
+        <v>20.3</v>
+      </c>
+      <c r="H101">
+        <v>712.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>13.1</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>12.1</v>
+      </c>
+      <c r="M101">
+        <v>173.1481488</v>
+      </c>
+      <c r="N101">
+        <v>-161.0481488</v>
+      </c>
+      <c r="O101">
+        <v>-56.36685208</v>
+      </c>
+      <c r="P101">
+        <v>-104.68129672</v>
+      </c>
+      <c r="Q101">
+        <v>-103.68129672</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.672885555746221</v>
+      </c>
+      <c r="T101">
+        <v>43.49435508331309</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02445882343733149</v>
+      </c>
+      <c r="W101">
+        <v>0.2329592329631653</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.06988235267808995</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
